--- a/assets/excel/2026_1-3-1.xlsx
+++ b/assets/excel/2026_1-3-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F557EA8F-5BCD-4B83-9765-36E3B4CB55B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B23221E-2E96-4D0F-8902-7A64903521FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{D0D36073-601B-4828-907B-11F573759D0C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{D0D36073-601B-4828-907B-11F573759D0C}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -147,9 +147,6 @@
   </si>
   <si>
     <t>Niedersächsisches Ministerium für Soziales, Gesundheit und Gleichstellung (Hrsg.),</t>
-  </si>
-  <si>
-    <t>© Landesamt für Statistik Niedersachsen, Hannover 2025,                                                                          </t>
   </si>
   <si>
     <t>Vervielfältigung und Verbreitung, auch auszugsweise, mit Quellenangabe gestattet.</t>
@@ -306,6 +303,9 @@
   </si>
   <si>
     <t>Niedersachsen</t>
+  </si>
+  <si>
+    <t>© Landesamt für Statistik Niedersachsen, Hannover 2026,                                                                          </t>
   </si>
 </sst>
 </file>
@@ -956,7 +956,7 @@
   <sheetData>
     <row r="1" spans="2:11" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C1" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="2:11" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1056,7 +1056,7 @@
         <v>101</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" s="12">
         <v>2025</v>
@@ -1088,7 +1088,7 @@
         <v>102</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" s="12">
         <v>2025</v>
@@ -1120,7 +1120,7 @@
         <v>103</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" s="12">
         <v>2025</v>
@@ -1152,7 +1152,7 @@
         <v>151</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" s="12">
         <v>2025</v>
@@ -1184,7 +1184,7 @@
         <v>153</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="12">
         <v>2025</v>
@@ -1216,7 +1216,7 @@
         <v>154</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" s="12">
         <v>2025</v>
@@ -1248,7 +1248,7 @@
         <v>155</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" s="12">
         <v>2025</v>
@@ -1280,7 +1280,7 @@
         <v>157</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="12">
         <v>2025</v>
@@ -1312,7 +1312,7 @@
         <v>158</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" s="12">
         <v>2025</v>
@@ -1344,7 +1344,7 @@
         <v>159</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D19" s="12">
         <v>2025</v>
@@ -1376,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D20" s="16">
         <v>2025</v>
@@ -1408,7 +1408,7 @@
         <v>241</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D21" s="12">
         <v>2025</v>
@@ -1440,7 +1440,7 @@
         <v>241001</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D22" s="12">
         <v>2025</v>
@@ -1472,7 +1472,7 @@
         <v>241999</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D23" s="12">
         <v>2025</v>
@@ -1504,7 +1504,7 @@
         <v>251</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" s="12">
         <v>2025</v>
@@ -1536,7 +1536,7 @@
         <v>252</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D25" s="12">
         <v>2025</v>
@@ -1568,7 +1568,7 @@
         <v>254</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" s="12">
         <v>2025</v>
@@ -1600,7 +1600,7 @@
         <v>255</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" s="12">
         <v>2025</v>
@@ -1632,7 +1632,7 @@
         <v>256</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D28" s="12">
         <v>2025</v>
@@ -1664,7 +1664,7 @@
         <v>257</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D29" s="12">
         <v>2025</v>
@@ -1696,7 +1696,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D30" s="16">
         <v>2025</v>
@@ -1728,7 +1728,7 @@
         <v>351</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D31" s="12">
         <v>2025</v>
@@ -1760,7 +1760,7 @@
         <v>352</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D32" s="12">
         <v>2025</v>
@@ -1792,7 +1792,7 @@
         <v>353</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D33" s="12">
         <v>2025</v>
@@ -1824,7 +1824,7 @@
         <v>12</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D34" s="12">
         <v>2025</v>
@@ -1856,7 +1856,7 @@
         <v>355</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D35" s="12">
         <v>2025</v>
@@ -1888,7 +1888,7 @@
         <v>356</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D36" s="12">
         <v>2025</v>
@@ -1920,7 +1920,7 @@
         <v>357</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D37" s="12">
         <v>2025</v>
@@ -1952,7 +1952,7 @@
         <v>358</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D38" s="12">
         <v>2025</v>
@@ -1984,7 +1984,7 @@
         <v>359</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D39" s="12">
         <v>2025</v>
@@ -2016,7 +2016,7 @@
         <v>12</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D40" s="12">
         <v>2025</v>
@@ -2048,7 +2048,7 @@
         <v>361</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D41" s="12">
         <v>2025</v>
@@ -2080,7 +2080,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D42" s="16">
         <v>2025</v>
@@ -2112,7 +2112,7 @@
         <v>401</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D43" s="12">
         <v>2025</v>
@@ -2144,7 +2144,7 @@
         <v>13</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D44" s="12">
         <v>2025</v>
@@ -2176,7 +2176,7 @@
         <v>403</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D45" s="12">
         <v>2025</v>
@@ -2208,7 +2208,7 @@
         <v>404</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D46" s="12">
         <v>2025</v>
@@ -2240,7 +2240,7 @@
         <v>405</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D47" s="12">
         <v>2025</v>
@@ -2272,7 +2272,7 @@
         <v>451</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D48" s="12">
         <v>2025</v>
@@ -2304,7 +2304,7 @@
         <v>452</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D49" s="12">
         <v>2025</v>
@@ -2336,7 +2336,7 @@
         <v>453</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D50" s="12">
         <v>2025</v>
@@ -2368,7 +2368,7 @@
         <v>454</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D51" s="12">
         <v>2025</v>
@@ -2400,7 +2400,7 @@
         <v>14</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D52" s="12">
         <v>2025</v>
@@ -2432,7 +2432,7 @@
         <v>456</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D53" s="12">
         <v>2025</v>
@@ -2464,7 +2464,7 @@
         <v>13</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D54" s="12">
         <v>2025</v>
@@ -2496,7 +2496,7 @@
         <v>458</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D55" s="12">
         <v>2025</v>
@@ -2528,7 +2528,7 @@
         <v>459</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D56" s="12">
         <v>2025</v>
@@ -2560,7 +2560,7 @@
         <v>460</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D57" s="12">
         <v>2025</v>
@@ -2592,7 +2592,7 @@
         <v>461</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D58" s="12">
         <v>2025</v>
@@ -2624,7 +2624,7 @@
         <v>14</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D59" s="12">
         <v>2025</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D60" s="16">
         <v>2025</v>
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D61" s="16">
         <v>2025</v>
@@ -2720,7 +2720,7 @@
         <v>101</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D62" s="12">
         <v>2024</v>
@@ -2752,7 +2752,7 @@
         <v>102</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D63" s="12">
         <v>2024</v>
@@ -2784,7 +2784,7 @@
         <v>103</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D64" s="12">
         <v>2024</v>
@@ -2816,7 +2816,7 @@
         <v>151</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D65" s="12">
         <v>2024</v>
@@ -2848,7 +2848,7 @@
         <v>153</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D66" s="12">
         <v>2024</v>
@@ -2880,7 +2880,7 @@
         <v>154</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D67" s="12">
         <v>2024</v>
@@ -2912,7 +2912,7 @@
         <v>155</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D68" s="12">
         <v>2024</v>
@@ -2944,7 +2944,7 @@
         <v>157</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D69" s="12">
         <v>2024</v>
@@ -2976,7 +2976,7 @@
         <v>158</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D70" s="12">
         <v>2024</v>
@@ -3008,7 +3008,7 @@
         <v>159</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D71" s="12">
         <v>2024</v>
@@ -3040,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D72" s="16">
         <v>2024</v>
@@ -3072,7 +3072,7 @@
         <v>241</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D73" s="12">
         <v>2024</v>
@@ -3104,7 +3104,7 @@
         <v>241001</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D74" s="12">
         <v>2024</v>
@@ -3136,7 +3136,7 @@
         <v>241999</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D75" s="12">
         <v>2024</v>
@@ -3168,7 +3168,7 @@
         <v>251</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D76" s="12">
         <v>2024</v>
@@ -3200,7 +3200,7 @@
         <v>252</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D77" s="12">
         <v>2024</v>
@@ -3232,7 +3232,7 @@
         <v>254</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D78" s="12">
         <v>2024</v>
@@ -3264,7 +3264,7 @@
         <v>255</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D79" s="12">
         <v>2024</v>
@@ -3296,7 +3296,7 @@
         <v>256</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D80" s="12">
         <v>2024</v>
@@ -3328,7 +3328,7 @@
         <v>257</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D81" s="12">
         <v>2024</v>
@@ -3360,7 +3360,7 @@
         <v>2</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D82" s="16">
         <v>2024</v>
@@ -3392,7 +3392,7 @@
         <v>351</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D83" s="12">
         <v>2024</v>
@@ -3424,7 +3424,7 @@
         <v>352</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D84" s="12">
         <v>2024</v>
@@ -3456,7 +3456,7 @@
         <v>353</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D85" s="12">
         <v>2024</v>
@@ -3488,7 +3488,7 @@
         <v>12</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D86" s="12">
         <v>2024</v>
@@ -3520,7 +3520,7 @@
         <v>355</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D87" s="12">
         <v>2024</v>
@@ -3552,7 +3552,7 @@
         <v>356</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D88" s="12">
         <v>2024</v>
@@ -3584,7 +3584,7 @@
         <v>357</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D89" s="12">
         <v>2024</v>
@@ -3616,7 +3616,7 @@
         <v>358</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D90" s="12">
         <v>2024</v>
@@ -3648,7 +3648,7 @@
         <v>359</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D91" s="12">
         <v>2024</v>
@@ -3680,7 +3680,7 @@
         <v>12</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D92" s="12">
         <v>2024</v>
@@ -3712,7 +3712,7 @@
         <v>361</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D93" s="12">
         <v>2024</v>
@@ -3744,7 +3744,7 @@
         <v>3</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D94" s="16">
         <v>2024</v>
@@ -3776,7 +3776,7 @@
         <v>401</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D95" s="12">
         <v>2024</v>
@@ -3808,7 +3808,7 @@
         <v>13</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D96" s="12">
         <v>2024</v>
@@ -3840,7 +3840,7 @@
         <v>403</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D97" s="12">
         <v>2024</v>
@@ -3872,7 +3872,7 @@
         <v>404</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D98" s="12">
         <v>2024</v>
@@ -3904,7 +3904,7 @@
         <v>405</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D99" s="12">
         <v>2024</v>
@@ -3936,7 +3936,7 @@
         <v>451</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D100" s="12">
         <v>2024</v>
@@ -3968,7 +3968,7 @@
         <v>452</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D101" s="12">
         <v>2024</v>
@@ -4000,7 +4000,7 @@
         <v>453</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D102" s="12">
         <v>2024</v>
@@ -4032,7 +4032,7 @@
         <v>454</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D103" s="12">
         <v>2024</v>
@@ -4064,7 +4064,7 @@
         <v>14</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D104" s="12">
         <v>2024</v>
@@ -4096,7 +4096,7 @@
         <v>456</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D105" s="12">
         <v>2024</v>
@@ -4128,7 +4128,7 @@
         <v>13</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D106" s="12">
         <v>2024</v>
@@ -4160,7 +4160,7 @@
         <v>458</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D107" s="12">
         <v>2024</v>
@@ -4192,7 +4192,7 @@
         <v>459</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D108" s="12">
         <v>2024</v>
@@ -4224,7 +4224,7 @@
         <v>460</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D109" s="12">
         <v>2024</v>
@@ -4256,7 +4256,7 @@
         <v>461</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D110" s="12">
         <v>2024</v>
@@ -4288,7 +4288,7 @@
         <v>14</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D111" s="12">
         <v>2024</v>
@@ -4320,7 +4320,7 @@
         <v>4</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D112" s="16">
         <v>2024</v>
@@ -4352,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D113" s="16">
         <v>2024</v>
@@ -4384,7 +4384,7 @@
         <v>101</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D114" s="12">
         <v>2023</v>
@@ -4416,7 +4416,7 @@
         <v>102</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D115" s="12">
         <v>2023</v>
@@ -4448,7 +4448,7 @@
         <v>103</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D116" s="12">
         <v>2023</v>
@@ -4480,7 +4480,7 @@
         <v>151</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D117" s="12">
         <v>2023</v>
@@ -4512,7 +4512,7 @@
         <v>153</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D118" s="12">
         <v>2023</v>
@@ -4544,7 +4544,7 @@
         <v>154</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D119" s="12">
         <v>2023</v>
@@ -4576,7 +4576,7 @@
         <v>155</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D120" s="12">
         <v>2023</v>
@@ -4608,7 +4608,7 @@
         <v>157</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D121" s="12">
         <v>2023</v>
@@ -4640,7 +4640,7 @@
         <v>158</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D122" s="12">
         <v>2023</v>
@@ -4672,7 +4672,7 @@
         <v>159</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D123" s="12">
         <v>2023</v>
@@ -4704,7 +4704,7 @@
         <v>1</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D124" s="16">
         <v>2023</v>
@@ -4736,7 +4736,7 @@
         <v>241</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D125" s="12">
         <v>2023</v>
@@ -4768,7 +4768,7 @@
         <v>241001</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D126" s="12">
         <v>2023</v>
@@ -4800,7 +4800,7 @@
         <v>241999</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D127" s="12">
         <v>2023</v>
@@ -4832,7 +4832,7 @@
         <v>251</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D128" s="12">
         <v>2023</v>
@@ -4864,7 +4864,7 @@
         <v>252</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D129" s="12">
         <v>2023</v>
@@ -4896,7 +4896,7 @@
         <v>254</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D130" s="12">
         <v>2023</v>
@@ -4928,7 +4928,7 @@
         <v>255</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D131" s="12">
         <v>2023</v>
@@ -4960,7 +4960,7 @@
         <v>256</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D132" s="12">
         <v>2023</v>
@@ -4992,7 +4992,7 @@
         <v>257</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D133" s="12">
         <v>2023</v>
@@ -5024,7 +5024,7 @@
         <v>2</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D134" s="16">
         <v>2023</v>
@@ -5056,7 +5056,7 @@
         <v>351</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D135" s="12">
         <v>2023</v>
@@ -5088,7 +5088,7 @@
         <v>352</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D136" s="12">
         <v>2023</v>
@@ -5120,7 +5120,7 @@
         <v>353</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D137" s="12">
         <v>2023</v>
@@ -5152,7 +5152,7 @@
         <v>12</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D138" s="12">
         <v>2023</v>
@@ -5184,7 +5184,7 @@
         <v>355</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D139" s="12">
         <v>2023</v>
@@ -5216,7 +5216,7 @@
         <v>356</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D140" s="12">
         <v>2023</v>
@@ -5248,7 +5248,7 @@
         <v>357</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D141" s="12">
         <v>2023</v>
@@ -5280,7 +5280,7 @@
         <v>358</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D142" s="12">
         <v>2023</v>
@@ -5312,7 +5312,7 @@
         <v>359</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D143" s="12">
         <v>2023</v>
@@ -5344,7 +5344,7 @@
         <v>12</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D144" s="12">
         <v>2023</v>
@@ -5376,7 +5376,7 @@
         <v>361</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D145" s="12">
         <v>2023</v>
@@ -5408,7 +5408,7 @@
         <v>3</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D146" s="16">
         <v>2023</v>
@@ -5440,7 +5440,7 @@
         <v>401</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D147" s="12">
         <v>2023</v>
@@ -5472,7 +5472,7 @@
         <v>13</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D148" s="12">
         <v>2023</v>
@@ -5504,7 +5504,7 @@
         <v>403</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D149" s="12">
         <v>2023</v>
@@ -5536,7 +5536,7 @@
         <v>404</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D150" s="12">
         <v>2023</v>
@@ -5568,7 +5568,7 @@
         <v>405</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D151" s="12">
         <v>2023</v>
@@ -5600,7 +5600,7 @@
         <v>451</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D152" s="12">
         <v>2023</v>
@@ -5632,7 +5632,7 @@
         <v>452</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D153" s="12">
         <v>2023</v>
@@ -5664,7 +5664,7 @@
         <v>453</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D154" s="12">
         <v>2023</v>
@@ -5696,7 +5696,7 @@
         <v>454</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D155" s="12">
         <v>2023</v>
@@ -5728,7 +5728,7 @@
         <v>14</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D156" s="12">
         <v>2023</v>
@@ -5760,7 +5760,7 @@
         <v>456</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D157" s="12">
         <v>2023</v>
@@ -5792,7 +5792,7 @@
         <v>13</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D158" s="12">
         <v>2023</v>
@@ -5824,7 +5824,7 @@
         <v>458</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D159" s="12">
         <v>2023</v>
@@ -5856,7 +5856,7 @@
         <v>459</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D160" s="12">
         <v>2023</v>
@@ -5888,7 +5888,7 @@
         <v>460</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D161" s="12">
         <v>2023</v>
@@ -5920,7 +5920,7 @@
         <v>461</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D162" s="12">
         <v>2023</v>
@@ -5952,7 +5952,7 @@
         <v>14</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D163" s="12">
         <v>2023</v>
@@ -5984,7 +5984,7 @@
         <v>4</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D164" s="16">
         <v>2023</v>
@@ -6016,7 +6016,7 @@
         <v>0</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D165" s="16">
         <v>2023</v>
@@ -6048,7 +6048,7 @@
         <v>101</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D166" s="12">
         <v>2022</v>
@@ -6080,7 +6080,7 @@
         <v>102</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D167" s="12">
         <v>2022</v>
@@ -6112,7 +6112,7 @@
         <v>103</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D168" s="12">
         <v>2022</v>
@@ -6144,7 +6144,7 @@
         <v>151</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D169" s="12">
         <v>2022</v>
@@ -6176,7 +6176,7 @@
         <v>153</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D170" s="12">
         <v>2022</v>
@@ -6208,7 +6208,7 @@
         <v>154</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D171" s="12">
         <v>2022</v>
@@ -6240,7 +6240,7 @@
         <v>155</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D172" s="12">
         <v>2022</v>
@@ -6272,7 +6272,7 @@
         <v>157</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D173" s="12">
         <v>2022</v>
@@ -6304,7 +6304,7 @@
         <v>158</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D174" s="12">
         <v>2022</v>
@@ -6336,7 +6336,7 @@
         <v>159</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D175" s="12">
         <v>2022</v>
@@ -6368,7 +6368,7 @@
         <v>1</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D176" s="16">
         <v>2022</v>
@@ -6400,7 +6400,7 @@
         <v>241</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D177" s="12">
         <v>2022</v>
@@ -6432,7 +6432,7 @@
         <v>241001</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D178" s="12">
         <v>2022</v>
@@ -6464,7 +6464,7 @@
         <v>241999</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D179" s="12">
         <v>2022</v>
@@ -6496,7 +6496,7 @@
         <v>251</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D180" s="12">
         <v>2022</v>
@@ -6528,7 +6528,7 @@
         <v>252</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D181" s="12">
         <v>2022</v>
@@ -6560,7 +6560,7 @@
         <v>254</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D182" s="12">
         <v>2022</v>
@@ -6592,7 +6592,7 @@
         <v>255</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D183" s="12">
         <v>2022</v>
@@ -6624,7 +6624,7 @@
         <v>256</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D184" s="12">
         <v>2022</v>
@@ -6656,7 +6656,7 @@
         <v>257</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D185" s="12">
         <v>2022</v>
@@ -6688,7 +6688,7 @@
         <v>2</v>
       </c>
       <c r="C186" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D186" s="16">
         <v>2022</v>
@@ -6720,7 +6720,7 @@
         <v>351</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D187" s="12">
         <v>2022</v>
@@ -6752,7 +6752,7 @@
         <v>352</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D188" s="12">
         <v>2022</v>
@@ -6784,7 +6784,7 @@
         <v>353</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D189" s="12">
         <v>2022</v>
@@ -6816,7 +6816,7 @@
         <v>12</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D190" s="12">
         <v>2022</v>
@@ -6848,7 +6848,7 @@
         <v>355</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D191" s="12">
         <v>2022</v>
@@ -6880,7 +6880,7 @@
         <v>356</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D192" s="12">
         <v>2022</v>
@@ -6912,7 +6912,7 @@
         <v>357</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D193" s="12">
         <v>2022</v>
@@ -6944,7 +6944,7 @@
         <v>358</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D194" s="12">
         <v>2022</v>
@@ -6976,7 +6976,7 @@
         <v>359</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D195" s="12">
         <v>2022</v>
@@ -7008,7 +7008,7 @@
         <v>12</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D196" s="12">
         <v>2022</v>
@@ -7040,7 +7040,7 @@
         <v>361</v>
       </c>
       <c r="C197" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D197" s="12">
         <v>2022</v>
@@ -7072,7 +7072,7 @@
         <v>3</v>
       </c>
       <c r="C198" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D198" s="16">
         <v>2022</v>
@@ -7104,7 +7104,7 @@
         <v>401</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D199" s="12">
         <v>2022</v>
@@ -7136,7 +7136,7 @@
         <v>13</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D200" s="12">
         <v>2022</v>
@@ -7168,7 +7168,7 @@
         <v>403</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D201" s="12">
         <v>2022</v>
@@ -7200,7 +7200,7 @@
         <v>404</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D202" s="12">
         <v>2022</v>
@@ -7232,7 +7232,7 @@
         <v>405</v>
       </c>
       <c r="C203" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D203" s="12">
         <v>2022</v>
@@ -7264,7 +7264,7 @@
         <v>451</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D204" s="12">
         <v>2022</v>
@@ -7296,7 +7296,7 @@
         <v>452</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D205" s="12">
         <v>2022</v>
@@ -7328,7 +7328,7 @@
         <v>453</v>
       </c>
       <c r="C206" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D206" s="12">
         <v>2022</v>
@@ -7360,7 +7360,7 @@
         <v>454</v>
       </c>
       <c r="C207" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D207" s="12">
         <v>2022</v>
@@ -7392,7 +7392,7 @@
         <v>14</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D208" s="12">
         <v>2022</v>
@@ -7424,7 +7424,7 @@
         <v>456</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D209" s="12">
         <v>2022</v>
@@ -7456,7 +7456,7 @@
         <v>13</v>
       </c>
       <c r="C210" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D210" s="12">
         <v>2022</v>
@@ -7488,7 +7488,7 @@
         <v>458</v>
       </c>
       <c r="C211" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D211" s="12">
         <v>2022</v>
@@ -7520,7 +7520,7 @@
         <v>459</v>
       </c>
       <c r="C212" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D212" s="12">
         <v>2022</v>
@@ -7552,7 +7552,7 @@
         <v>460</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D213" s="12">
         <v>2022</v>
@@ -7584,7 +7584,7 @@
         <v>461</v>
       </c>
       <c r="C214" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D214" s="12">
         <v>2022</v>
@@ -7616,7 +7616,7 @@
         <v>14</v>
       </c>
       <c r="C215" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D215" s="12">
         <v>2022</v>
@@ -7648,7 +7648,7 @@
         <v>4</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D216" s="16">
         <v>2022</v>
@@ -7680,7 +7680,7 @@
         <v>0</v>
       </c>
       <c r="C217" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D217" s="16">
         <v>2022</v>
@@ -7712,7 +7712,7 @@
         <v>101</v>
       </c>
       <c r="C218" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D218" s="16">
         <v>2021</v>
@@ -7744,7 +7744,7 @@
         <v>102</v>
       </c>
       <c r="C219" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D219" s="20">
         <v>2021</v>
@@ -7776,7 +7776,7 @@
         <v>103</v>
       </c>
       <c r="C220" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D220" s="20">
         <v>2021</v>
@@ -7808,7 +7808,7 @@
         <v>151</v>
       </c>
       <c r="C221" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D221" s="20">
         <v>2021</v>
@@ -7840,7 +7840,7 @@
         <v>153</v>
       </c>
       <c r="C222" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D222" s="20">
         <v>2021</v>
@@ -7872,7 +7872,7 @@
         <v>154</v>
       </c>
       <c r="C223" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D223" s="20">
         <v>2021</v>
@@ -7904,7 +7904,7 @@
         <v>155</v>
       </c>
       <c r="C224" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D224" s="20">
         <v>2021</v>
@@ -7936,7 +7936,7 @@
         <v>157</v>
       </c>
       <c r="C225" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D225" s="20">
         <v>2021</v>
@@ -7968,7 +7968,7 @@
         <v>158</v>
       </c>
       <c r="C226" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D226" s="20">
         <v>2021</v>
@@ -8000,7 +8000,7 @@
         <v>159</v>
       </c>
       <c r="C227" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D227" s="20">
         <v>2021</v>
@@ -8032,7 +8032,7 @@
         <v>1</v>
       </c>
       <c r="C228" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D228" s="20">
         <v>2021</v>
@@ -8064,7 +8064,7 @@
         <v>241</v>
       </c>
       <c r="C229" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D229" s="16">
         <v>2021</v>
@@ -8096,7 +8096,7 @@
         <v>241001</v>
       </c>
       <c r="C230" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D230" s="20">
         <v>2021</v>
@@ -8128,7 +8128,7 @@
         <v>241999</v>
       </c>
       <c r="C231" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D231" s="20">
         <v>2021</v>
@@ -8160,7 +8160,7 @@
         <v>251</v>
       </c>
       <c r="C232" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D232" s="20">
         <v>2021</v>
@@ -8192,7 +8192,7 @@
         <v>252</v>
       </c>
       <c r="C233" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D233" s="20">
         <v>2021</v>
@@ -8224,7 +8224,7 @@
         <v>254</v>
       </c>
       <c r="C234" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D234" s="20">
         <v>2021</v>
@@ -8256,7 +8256,7 @@
         <v>255</v>
       </c>
       <c r="C235" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D235" s="20">
         <v>2021</v>
@@ -8288,7 +8288,7 @@
         <v>256</v>
       </c>
       <c r="C236" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D236" s="20">
         <v>2021</v>
@@ -8320,7 +8320,7 @@
         <v>257</v>
       </c>
       <c r="C237" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D237" s="20">
         <v>2021</v>
@@ -8352,7 +8352,7 @@
         <v>2</v>
       </c>
       <c r="C238" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D238" s="20">
         <v>2021</v>
@@ -8384,7 +8384,7 @@
         <v>351</v>
       </c>
       <c r="C239" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D239" s="16">
         <v>2021</v>
@@ -8416,7 +8416,7 @@
         <v>352</v>
       </c>
       <c r="C240" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D240" s="20">
         <v>2021</v>
@@ -8448,7 +8448,7 @@
         <v>353</v>
       </c>
       <c r="C241" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D241" s="20">
         <v>2021</v>
@@ -8480,7 +8480,7 @@
         <v>12</v>
       </c>
       <c r="C242" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D242" s="20">
         <v>2021</v>
@@ -8512,7 +8512,7 @@
         <v>355</v>
       </c>
       <c r="C243" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D243" s="20">
         <v>2021</v>
@@ -8544,7 +8544,7 @@
         <v>356</v>
       </c>
       <c r="C244" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D244" s="20">
         <v>2021</v>
@@ -8576,7 +8576,7 @@
         <v>357</v>
       </c>
       <c r="C245" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D245" s="20">
         <v>2021</v>
@@ -8608,7 +8608,7 @@
         <v>358</v>
       </c>
       <c r="C246" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D246" s="20">
         <v>2021</v>
@@ -8640,7 +8640,7 @@
         <v>359</v>
       </c>
       <c r="C247" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D247" s="20">
         <v>2021</v>
@@ -8672,7 +8672,7 @@
         <v>12</v>
       </c>
       <c r="C248" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D248" s="20">
         <v>2021</v>
@@ -8704,7 +8704,7 @@
         <v>361</v>
       </c>
       <c r="C249" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D249" s="20">
         <v>2021</v>
@@ -8736,7 +8736,7 @@
         <v>3</v>
       </c>
       <c r="C250" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D250" s="20">
         <v>2021</v>
@@ -8768,7 +8768,7 @@
         <v>401</v>
       </c>
       <c r="C251" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D251" s="16">
         <v>2021</v>
@@ -8800,7 +8800,7 @@
         <v>13</v>
       </c>
       <c r="C252" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D252" s="20">
         <v>2021</v>
@@ -8832,7 +8832,7 @@
         <v>403</v>
       </c>
       <c r="C253" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D253" s="20">
         <v>2021</v>
@@ -8864,7 +8864,7 @@
         <v>404</v>
       </c>
       <c r="C254" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D254" s="20">
         <v>2021</v>
@@ -8896,7 +8896,7 @@
         <v>405</v>
       </c>
       <c r="C255" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D255" s="20">
         <v>2021</v>
@@ -8928,7 +8928,7 @@
         <v>451</v>
       </c>
       <c r="C256" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D256" s="20">
         <v>2021</v>
@@ -8960,7 +8960,7 @@
         <v>452</v>
       </c>
       <c r="C257" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D257" s="20">
         <v>2021</v>
@@ -8992,7 +8992,7 @@
         <v>453</v>
       </c>
       <c r="C258" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D258" s="20">
         <v>2021</v>
@@ -9024,7 +9024,7 @@
         <v>454</v>
       </c>
       <c r="C259" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D259" s="20">
         <v>2021</v>
@@ -9056,7 +9056,7 @@
         <v>14</v>
       </c>
       <c r="C260" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D260" s="20">
         <v>2021</v>
@@ -9088,7 +9088,7 @@
         <v>456</v>
       </c>
       <c r="C261" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D261" s="20">
         <v>2021</v>
@@ -9120,7 +9120,7 @@
         <v>13</v>
       </c>
       <c r="C262" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D262" s="20">
         <v>2021</v>
@@ -9152,7 +9152,7 @@
         <v>458</v>
       </c>
       <c r="C263" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D263" s="20">
         <v>2021</v>
@@ -9184,7 +9184,7 @@
         <v>459</v>
       </c>
       <c r="C264" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D264" s="20">
         <v>2021</v>
@@ -9216,7 +9216,7 @@
         <v>460</v>
       </c>
       <c r="C265" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D265" s="20">
         <v>2021</v>
@@ -9248,7 +9248,7 @@
         <v>461</v>
       </c>
       <c r="C266" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D266" s="20">
         <v>2021</v>
@@ -9280,7 +9280,7 @@
         <v>14</v>
       </c>
       <c r="C267" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D267" s="20">
         <v>2021</v>
@@ -9312,7 +9312,7 @@
         <v>4</v>
       </c>
       <c r="C268" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D268" s="20">
         <v>2021</v>
@@ -9344,7 +9344,7 @@
         <v>0</v>
       </c>
       <c r="C269" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D269" s="16">
         <v>2021</v>
@@ -9376,7 +9376,7 @@
         <v>0</v>
       </c>
       <c r="C270" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D270" s="16">
         <v>2020</v>
@@ -9408,7 +9408,7 @@
         <v>101</v>
       </c>
       <c r="C271" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D271" s="20">
         <v>2019</v>
@@ -9440,7 +9440,7 @@
         <v>102</v>
       </c>
       <c r="C272" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D272" s="20">
         <v>2019</v>
@@ -9472,7 +9472,7 @@
         <v>103</v>
       </c>
       <c r="C273" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D273" s="20">
         <v>2019</v>
@@ -9504,7 +9504,7 @@
         <v>151</v>
       </c>
       <c r="C274" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D274" s="20">
         <v>2019</v>
@@ -9536,7 +9536,7 @@
         <v>153</v>
       </c>
       <c r="C275" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D275" s="20">
         <v>2019</v>
@@ -9568,7 +9568,7 @@
         <v>154</v>
       </c>
       <c r="C276" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D276" s="20">
         <v>2019</v>
@@ -9600,7 +9600,7 @@
         <v>155</v>
       </c>
       <c r="C277" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D277" s="20">
         <v>2019</v>
@@ -9632,7 +9632,7 @@
         <v>157</v>
       </c>
       <c r="C278" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D278" s="20">
         <v>2019</v>
@@ -9664,7 +9664,7 @@
         <v>158</v>
       </c>
       <c r="C279" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D279" s="20">
         <v>2019</v>
@@ -9696,7 +9696,7 @@
         <v>159</v>
       </c>
       <c r="C280" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D280" s="20">
         <v>2019</v>
@@ -9728,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="C281" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D281" s="16">
         <v>2019</v>
@@ -9760,7 +9760,7 @@
         <v>241</v>
       </c>
       <c r="C282" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D282" s="20">
         <v>2019</v>
@@ -9792,7 +9792,7 @@
         <v>241001</v>
       </c>
       <c r="C283" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D283" s="20">
         <v>2019</v>
@@ -9824,7 +9824,7 @@
         <v>241999</v>
       </c>
       <c r="C284" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D284" s="20">
         <v>2019</v>
@@ -9856,7 +9856,7 @@
         <v>251</v>
       </c>
       <c r="C285" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D285" s="20">
         <v>2019</v>
@@ -9888,7 +9888,7 @@
         <v>252</v>
       </c>
       <c r="C286" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D286" s="20">
         <v>2019</v>
@@ -9920,7 +9920,7 @@
         <v>254</v>
       </c>
       <c r="C287" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D287" s="20">
         <v>2019</v>
@@ -9952,7 +9952,7 @@
         <v>255</v>
       </c>
       <c r="C288" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D288" s="20">
         <v>2019</v>
@@ -9984,7 +9984,7 @@
         <v>256</v>
       </c>
       <c r="C289" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D289" s="20">
         <v>2019</v>
@@ -10016,7 +10016,7 @@
         <v>257</v>
       </c>
       <c r="C290" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D290" s="20">
         <v>2019</v>
@@ -10048,7 +10048,7 @@
         <v>2</v>
       </c>
       <c r="C291" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D291" s="16">
         <v>2019</v>
@@ -10080,7 +10080,7 @@
         <v>351</v>
       </c>
       <c r="C292" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D292" s="20">
         <v>2019</v>
@@ -10112,7 +10112,7 @@
         <v>352</v>
       </c>
       <c r="C293" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D293" s="20">
         <v>2019</v>
@@ -10144,7 +10144,7 @@
         <v>353</v>
       </c>
       <c r="C294" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D294" s="20">
         <v>2019</v>
@@ -10176,7 +10176,7 @@
         <v>12</v>
       </c>
       <c r="C295" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D295" s="20">
         <v>2019</v>
@@ -10208,7 +10208,7 @@
         <v>355</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D296" s="20">
         <v>2019</v>
@@ -10240,7 +10240,7 @@
         <v>356</v>
       </c>
       <c r="C297" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D297" s="20">
         <v>2019</v>
@@ -10272,7 +10272,7 @@
         <v>357</v>
       </c>
       <c r="C298" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D298" s="20">
         <v>2019</v>
@@ -10304,7 +10304,7 @@
         <v>358</v>
       </c>
       <c r="C299" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D299" s="20">
         <v>2019</v>
@@ -10336,7 +10336,7 @@
         <v>359</v>
       </c>
       <c r="C300" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D300" s="20">
         <v>2019</v>
@@ -10368,7 +10368,7 @@
         <v>12</v>
       </c>
       <c r="C301" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D301" s="20">
         <v>2019</v>
@@ -10400,7 +10400,7 @@
         <v>361</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D302" s="20">
         <v>2019</v>
@@ -10432,7 +10432,7 @@
         <v>3</v>
       </c>
       <c r="C303" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D303" s="16">
         <v>2019</v>
@@ -10464,7 +10464,7 @@
         <v>401</v>
       </c>
       <c r="C304" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D304" s="20">
         <v>2019</v>
@@ -10496,7 +10496,7 @@
         <v>13</v>
       </c>
       <c r="C305" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D305" s="20">
         <v>2019</v>
@@ -10528,7 +10528,7 @@
         <v>403</v>
       </c>
       <c r="C306" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D306" s="20">
         <v>2019</v>
@@ -10560,7 +10560,7 @@
         <v>404</v>
       </c>
       <c r="C307" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D307" s="20">
         <v>2019</v>
@@ -10592,7 +10592,7 @@
         <v>405</v>
       </c>
       <c r="C308" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D308" s="20">
         <v>2019</v>
@@ -10624,7 +10624,7 @@
         <v>451</v>
       </c>
       <c r="C309" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D309" s="20">
         <v>2019</v>
@@ -10656,7 +10656,7 @@
         <v>452</v>
       </c>
       <c r="C310" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D310" s="20">
         <v>2019</v>
@@ -10688,7 +10688,7 @@
         <v>453</v>
       </c>
       <c r="C311" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D311" s="20">
         <v>2019</v>
@@ -10720,7 +10720,7 @@
         <v>454</v>
       </c>
       <c r="C312" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D312" s="20">
         <v>2019</v>
@@ -10752,7 +10752,7 @@
         <v>14</v>
       </c>
       <c r="C313" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D313" s="20">
         <v>2019</v>
@@ -10784,7 +10784,7 @@
         <v>456</v>
       </c>
       <c r="C314" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D314" s="20">
         <v>2019</v>
@@ -10816,7 +10816,7 @@
         <v>13</v>
       </c>
       <c r="C315" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D315" s="20">
         <v>2019</v>
@@ -10848,7 +10848,7 @@
         <v>458</v>
       </c>
       <c r="C316" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D316" s="20">
         <v>2019</v>
@@ -10880,7 +10880,7 @@
         <v>459</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D317" s="20">
         <v>2019</v>
@@ -10912,7 +10912,7 @@
         <v>460</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D318" s="20">
         <v>2019</v>
@@ -10944,7 +10944,7 @@
         <v>461</v>
       </c>
       <c r="C319" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D319" s="20">
         <v>2019</v>
@@ -10976,7 +10976,7 @@
         <v>14</v>
       </c>
       <c r="C320" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D320" s="20">
         <v>2019</v>
@@ -11008,7 +11008,7 @@
         <v>4</v>
       </c>
       <c r="C321" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D321" s="16">
         <v>2019</v>
@@ -11040,7 +11040,7 @@
         <v>0</v>
       </c>
       <c r="C322" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D322" s="16">
         <v>2019</v>
@@ -11072,7 +11072,7 @@
         <v>101</v>
       </c>
       <c r="C323" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D323" s="20">
         <v>2018</v>
@@ -11104,7 +11104,7 @@
         <v>102</v>
       </c>
       <c r="C324" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D324" s="20">
         <v>2018</v>
@@ -11136,7 +11136,7 @@
         <v>103</v>
       </c>
       <c r="C325" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D325" s="20">
         <v>2018</v>
@@ -11168,7 +11168,7 @@
         <v>151</v>
       </c>
       <c r="C326" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D326" s="20">
         <v>2018</v>
@@ -11200,7 +11200,7 @@
         <v>153</v>
       </c>
       <c r="C327" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D327" s="20">
         <v>2018</v>
@@ -11232,7 +11232,7 @@
         <v>154</v>
       </c>
       <c r="C328" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D328" s="20">
         <v>2018</v>
@@ -11264,7 +11264,7 @@
         <v>155</v>
       </c>
       <c r="C329" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D329" s="20">
         <v>2018</v>
@@ -11296,7 +11296,7 @@
         <v>157</v>
       </c>
       <c r="C330" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D330" s="20">
         <v>2018</v>
@@ -11328,7 +11328,7 @@
         <v>158</v>
       </c>
       <c r="C331" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D331" s="20">
         <v>2018</v>
@@ -11360,7 +11360,7 @@
         <v>159</v>
       </c>
       <c r="C332" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D332" s="20">
         <v>2018</v>
@@ -11392,7 +11392,7 @@
         <v>1</v>
       </c>
       <c r="C333" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D333" s="16">
         <v>2018</v>
@@ -11424,7 +11424,7 @@
         <v>241</v>
       </c>
       <c r="C334" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D334" s="20">
         <v>2018</v>
@@ -11456,7 +11456,7 @@
         <v>241001</v>
       </c>
       <c r="C335" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D335" s="20">
         <v>2018</v>
@@ -11488,7 +11488,7 @@
         <v>241999</v>
       </c>
       <c r="C336" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D336" s="20">
         <v>2018</v>
@@ -11520,7 +11520,7 @@
         <v>251</v>
       </c>
       <c r="C337" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D337" s="20">
         <v>2018</v>
@@ -11552,7 +11552,7 @@
         <v>252</v>
       </c>
       <c r="C338" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D338" s="20">
         <v>2018</v>
@@ -11584,7 +11584,7 @@
         <v>254</v>
       </c>
       <c r="C339" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D339" s="20">
         <v>2018</v>
@@ -11616,7 +11616,7 @@
         <v>255</v>
       </c>
       <c r="C340" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D340" s="20">
         <v>2018</v>
@@ -11648,7 +11648,7 @@
         <v>256</v>
       </c>
       <c r="C341" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D341" s="20">
         <v>2018</v>
@@ -11680,7 +11680,7 @@
         <v>257</v>
       </c>
       <c r="C342" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D342" s="20">
         <v>2018</v>
@@ -11712,7 +11712,7 @@
         <v>2</v>
       </c>
       <c r="C343" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D343" s="16">
         <v>2018</v>
@@ -11744,7 +11744,7 @@
         <v>351</v>
       </c>
       <c r="C344" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D344" s="20">
         <v>2018</v>
@@ -11776,7 +11776,7 @@
         <v>352</v>
       </c>
       <c r="C345" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D345" s="20">
         <v>2018</v>
@@ -11808,7 +11808,7 @@
         <v>353</v>
       </c>
       <c r="C346" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D346" s="20">
         <v>2018</v>
@@ -11840,7 +11840,7 @@
         <v>12</v>
       </c>
       <c r="C347" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D347" s="20">
         <v>2018</v>
@@ -11872,7 +11872,7 @@
         <v>355</v>
       </c>
       <c r="C348" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D348" s="20">
         <v>2018</v>
@@ -11904,7 +11904,7 @@
         <v>356</v>
       </c>
       <c r="C349" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D349" s="20">
         <v>2018</v>
@@ -11936,7 +11936,7 @@
         <v>357</v>
       </c>
       <c r="C350" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D350" s="20">
         <v>2018</v>
@@ -11968,7 +11968,7 @@
         <v>358</v>
       </c>
       <c r="C351" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D351" s="20">
         <v>2018</v>
@@ -12000,7 +12000,7 @@
         <v>359</v>
       </c>
       <c r="C352" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D352" s="20">
         <v>2018</v>
@@ -12032,7 +12032,7 @@
         <v>12</v>
       </c>
       <c r="C353" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D353" s="20">
         <v>2018</v>
@@ -12064,7 +12064,7 @@
         <v>361</v>
       </c>
       <c r="C354" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D354" s="20">
         <v>2018</v>
@@ -12096,7 +12096,7 @@
         <v>3</v>
       </c>
       <c r="C355" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D355" s="16">
         <v>2018</v>
@@ -12128,7 +12128,7 @@
         <v>401</v>
       </c>
       <c r="C356" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D356" s="20">
         <v>2018</v>
@@ -12160,7 +12160,7 @@
         <v>13</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D357" s="20">
         <v>2018</v>
@@ -12192,7 +12192,7 @@
         <v>403</v>
       </c>
       <c r="C358" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D358" s="20">
         <v>2018</v>
@@ -12224,7 +12224,7 @@
         <v>404</v>
       </c>
       <c r="C359" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D359" s="20">
         <v>2018</v>
@@ -12256,7 +12256,7 @@
         <v>405</v>
       </c>
       <c r="C360" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D360" s="20">
         <v>2018</v>
@@ -12288,7 +12288,7 @@
         <v>451</v>
       </c>
       <c r="C361" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D361" s="20">
         <v>2018</v>
@@ -12320,7 +12320,7 @@
         <v>452</v>
       </c>
       <c r="C362" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D362" s="20">
         <v>2018</v>
@@ -12352,7 +12352,7 @@
         <v>453</v>
       </c>
       <c r="C363" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D363" s="20">
         <v>2018</v>
@@ -12384,7 +12384,7 @@
         <v>454</v>
       </c>
       <c r="C364" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D364" s="20">
         <v>2018</v>
@@ -12416,7 +12416,7 @@
         <v>14</v>
       </c>
       <c r="C365" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D365" s="20">
         <v>2018</v>
@@ -12448,7 +12448,7 @@
         <v>456</v>
       </c>
       <c r="C366" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D366" s="20">
         <v>2018</v>
@@ -12480,7 +12480,7 @@
         <v>13</v>
       </c>
       <c r="C367" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D367" s="20">
         <v>2018</v>
@@ -12512,7 +12512,7 @@
         <v>458</v>
       </c>
       <c r="C368" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D368" s="20">
         <v>2018</v>
@@ -12544,7 +12544,7 @@
         <v>459</v>
       </c>
       <c r="C369" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D369" s="20">
         <v>2018</v>
@@ -12576,7 +12576,7 @@
         <v>460</v>
       </c>
       <c r="C370" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D370" s="20">
         <v>2018</v>
@@ -12608,7 +12608,7 @@
         <v>461</v>
       </c>
       <c r="C371" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D371" s="20">
         <v>2018</v>
@@ -12640,7 +12640,7 @@
         <v>14</v>
       </c>
       <c r="C372" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D372" s="20">
         <v>2018</v>
@@ -12672,7 +12672,7 @@
         <v>4</v>
       </c>
       <c r="C373" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D373" s="16">
         <v>2018</v>
@@ -12704,7 +12704,7 @@
         <v>0</v>
       </c>
       <c r="C374" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D374" s="16">
         <v>2018</v>
@@ -12736,7 +12736,7 @@
         <v>101</v>
       </c>
       <c r="C375" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D375" s="20">
         <v>2017</v>
@@ -12768,7 +12768,7 @@
         <v>102</v>
       </c>
       <c r="C376" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D376" s="20">
         <v>2017</v>
@@ -12800,7 +12800,7 @@
         <v>103</v>
       </c>
       <c r="C377" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D377" s="20">
         <v>2017</v>
@@ -12832,7 +12832,7 @@
         <v>151</v>
       </c>
       <c r="C378" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D378" s="20">
         <v>2017</v>
@@ -12864,7 +12864,7 @@
         <v>153</v>
       </c>
       <c r="C379" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D379" s="20">
         <v>2017</v>
@@ -12896,7 +12896,7 @@
         <v>154</v>
       </c>
       <c r="C380" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D380" s="20">
         <v>2017</v>
@@ -12928,7 +12928,7 @@
         <v>155</v>
       </c>
       <c r="C381" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D381" s="20">
         <v>2017</v>
@@ -12960,7 +12960,7 @@
         <v>157</v>
       </c>
       <c r="C382" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D382" s="20">
         <v>2017</v>
@@ -12992,7 +12992,7 @@
         <v>158</v>
       </c>
       <c r="C383" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D383" s="20">
         <v>2017</v>
@@ -13024,7 +13024,7 @@
         <v>159</v>
       </c>
       <c r="C384" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D384" s="20">
         <v>2017</v>
@@ -13056,7 +13056,7 @@
         <v>1</v>
       </c>
       <c r="C385" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D385" s="16">
         <v>2017</v>
@@ -13088,7 +13088,7 @@
         <v>241</v>
       </c>
       <c r="C386" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D386" s="20">
         <v>2017</v>
@@ -13120,7 +13120,7 @@
         <v>241001</v>
       </c>
       <c r="C387" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D387" s="20">
         <v>2017</v>
@@ -13152,7 +13152,7 @@
         <v>241999</v>
       </c>
       <c r="C388" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D388" s="20">
         <v>2017</v>
@@ -13184,7 +13184,7 @@
         <v>251</v>
       </c>
       <c r="C389" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D389" s="20">
         <v>2017</v>
@@ -13216,7 +13216,7 @@
         <v>252</v>
       </c>
       <c r="C390" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D390" s="20">
         <v>2017</v>
@@ -13248,7 +13248,7 @@
         <v>254</v>
       </c>
       <c r="C391" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D391" s="20">
         <v>2017</v>
@@ -13280,7 +13280,7 @@
         <v>255</v>
       </c>
       <c r="C392" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D392" s="20">
         <v>2017</v>
@@ -13312,7 +13312,7 @@
         <v>256</v>
       </c>
       <c r="C393" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D393" s="20">
         <v>2017</v>
@@ -13344,7 +13344,7 @@
         <v>257</v>
       </c>
       <c r="C394" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D394" s="20">
         <v>2017</v>
@@ -13376,7 +13376,7 @@
         <v>2</v>
       </c>
       <c r="C395" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D395" s="16">
         <v>2017</v>
@@ -13408,7 +13408,7 @@
         <v>351</v>
       </c>
       <c r="C396" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D396" s="20">
         <v>2017</v>
@@ -13440,7 +13440,7 @@
         <v>352</v>
       </c>
       <c r="C397" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D397" s="20">
         <v>2017</v>
@@ -13472,7 +13472,7 @@
         <v>353</v>
       </c>
       <c r="C398" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D398" s="20">
         <v>2017</v>
@@ -13504,7 +13504,7 @@
         <v>12</v>
       </c>
       <c r="C399" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D399" s="20">
         <v>2017</v>
@@ -13536,7 +13536,7 @@
         <v>355</v>
       </c>
       <c r="C400" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D400" s="20">
         <v>2017</v>
@@ -13568,7 +13568,7 @@
         <v>356</v>
       </c>
       <c r="C401" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D401" s="20">
         <v>2017</v>
@@ -13600,7 +13600,7 @@
         <v>357</v>
       </c>
       <c r="C402" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D402" s="20">
         <v>2017</v>
@@ -13632,7 +13632,7 @@
         <v>358</v>
       </c>
       <c r="C403" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D403" s="20">
         <v>2017</v>
@@ -13664,7 +13664,7 @@
         <v>359</v>
       </c>
       <c r="C404" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D404" s="20">
         <v>2017</v>
@@ -13696,7 +13696,7 @@
         <v>12</v>
       </c>
       <c r="C405" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D405" s="20">
         <v>2017</v>
@@ -13728,7 +13728,7 @@
         <v>361</v>
       </c>
       <c r="C406" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D406" s="20">
         <v>2017</v>
@@ -13760,7 +13760,7 @@
         <v>3</v>
       </c>
       <c r="C407" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D407" s="16">
         <v>2017</v>
@@ -13792,7 +13792,7 @@
         <v>401</v>
       </c>
       <c r="C408" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D408" s="20">
         <v>2017</v>
@@ -13824,7 +13824,7 @@
         <v>13</v>
       </c>
       <c r="C409" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D409" s="20">
         <v>2017</v>
@@ -13856,7 +13856,7 @@
         <v>403</v>
       </c>
       <c r="C410" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D410" s="20">
         <v>2017</v>
@@ -13888,7 +13888,7 @@
         <v>404</v>
       </c>
       <c r="C411" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D411" s="20">
         <v>2017</v>
@@ -13920,7 +13920,7 @@
         <v>405</v>
       </c>
       <c r="C412" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D412" s="20">
         <v>2017</v>
@@ -13952,7 +13952,7 @@
         <v>451</v>
       </c>
       <c r="C413" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D413" s="20">
         <v>2017</v>
@@ -13984,7 +13984,7 @@
         <v>452</v>
       </c>
       <c r="C414" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D414" s="20">
         <v>2017</v>
@@ -14016,7 +14016,7 @@
         <v>453</v>
       </c>
       <c r="C415" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D415" s="20">
         <v>2017</v>
@@ -14048,7 +14048,7 @@
         <v>454</v>
       </c>
       <c r="C416" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D416" s="20">
         <v>2017</v>
@@ -14080,7 +14080,7 @@
         <v>14</v>
       </c>
       <c r="C417" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D417" s="20">
         <v>2017</v>
@@ -14112,7 +14112,7 @@
         <v>456</v>
       </c>
       <c r="C418" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D418" s="20">
         <v>2017</v>
@@ -14144,7 +14144,7 @@
         <v>13</v>
       </c>
       <c r="C419" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D419" s="20">
         <v>2017</v>
@@ -14176,7 +14176,7 @@
         <v>458</v>
       </c>
       <c r="C420" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D420" s="20">
         <v>2017</v>
@@ -14208,7 +14208,7 @@
         <v>459</v>
       </c>
       <c r="C421" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D421" s="20">
         <v>2017</v>
@@ -14240,7 +14240,7 @@
         <v>460</v>
       </c>
       <c r="C422" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D422" s="20">
         <v>2017</v>
@@ -14272,7 +14272,7 @@
         <v>461</v>
       </c>
       <c r="C423" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D423" s="20">
         <v>2017</v>
@@ -14304,7 +14304,7 @@
         <v>14</v>
       </c>
       <c r="C424" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D424" s="20">
         <v>2017</v>
@@ -14336,7 +14336,7 @@
         <v>4</v>
       </c>
       <c r="C425" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D425" s="16">
         <v>2017</v>
@@ -14368,7 +14368,7 @@
         <v>0</v>
       </c>
       <c r="C426" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D426" s="16">
         <v>2017</v>
@@ -14400,7 +14400,7 @@
         <v>101</v>
       </c>
       <c r="C427" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D427" s="20">
         <v>2016</v>
@@ -14432,7 +14432,7 @@
         <v>102</v>
       </c>
       <c r="C428" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D428" s="20">
         <v>2016</v>
@@ -14464,7 +14464,7 @@
         <v>103</v>
       </c>
       <c r="C429" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D429" s="20">
         <v>2016</v>
@@ -14496,7 +14496,7 @@
         <v>151</v>
       </c>
       <c r="C430" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D430" s="20">
         <v>2016</v>
@@ -14528,7 +14528,7 @@
         <v>153</v>
       </c>
       <c r="C431" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D431" s="20">
         <v>2016</v>
@@ -14560,7 +14560,7 @@
         <v>154</v>
       </c>
       <c r="C432" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D432" s="20">
         <v>2016</v>
@@ -14592,7 +14592,7 @@
         <v>155</v>
       </c>
       <c r="C433" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D433" s="20">
         <v>2016</v>
@@ -14624,7 +14624,7 @@
         <v>157</v>
       </c>
       <c r="C434" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D434" s="20">
         <v>2016</v>
@@ -14656,7 +14656,7 @@
         <v>158</v>
       </c>
       <c r="C435" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D435" s="20">
         <v>2016</v>
@@ -14688,7 +14688,7 @@
         <v>159</v>
       </c>
       <c r="C436" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D436" s="20">
         <v>2016</v>
@@ -14720,7 +14720,7 @@
         <v>1</v>
       </c>
       <c r="C437" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D437" s="16">
         <v>2016</v>
@@ -14752,7 +14752,7 @@
         <v>241</v>
       </c>
       <c r="C438" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D438" s="20">
         <v>2016</v>
@@ -14784,7 +14784,7 @@
         <v>241001</v>
       </c>
       <c r="C439" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D439" s="20">
         <v>2016</v>
@@ -14816,7 +14816,7 @@
         <v>241999</v>
       </c>
       <c r="C440" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D440" s="20">
         <v>2016</v>
@@ -14848,7 +14848,7 @@
         <v>251</v>
       </c>
       <c r="C441" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D441" s="20">
         <v>2016</v>
@@ -14880,7 +14880,7 @@
         <v>252</v>
       </c>
       <c r="C442" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D442" s="20">
         <v>2016</v>
@@ -14912,7 +14912,7 @@
         <v>254</v>
       </c>
       <c r="C443" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D443" s="20">
         <v>2016</v>
@@ -14944,7 +14944,7 @@
         <v>255</v>
       </c>
       <c r="C444" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D444" s="20">
         <v>2016</v>
@@ -14976,7 +14976,7 @@
         <v>256</v>
       </c>
       <c r="C445" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D445" s="20">
         <v>2016</v>
@@ -15008,7 +15008,7 @@
         <v>257</v>
       </c>
       <c r="C446" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D446" s="20">
         <v>2016</v>
@@ -15040,7 +15040,7 @@
         <v>2</v>
       </c>
       <c r="C447" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D447" s="16">
         <v>2016</v>
@@ -15072,7 +15072,7 @@
         <v>351</v>
       </c>
       <c r="C448" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D448" s="20">
         <v>2016</v>
@@ -15104,7 +15104,7 @@
         <v>352</v>
       </c>
       <c r="C449" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D449" s="20">
         <v>2016</v>
@@ -15136,7 +15136,7 @@
         <v>353</v>
       </c>
       <c r="C450" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D450" s="20">
         <v>2016</v>
@@ -15168,7 +15168,7 @@
         <v>12</v>
       </c>
       <c r="C451" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D451" s="20">
         <v>2016</v>
@@ -15200,7 +15200,7 @@
         <v>355</v>
       </c>
       <c r="C452" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D452" s="20">
         <v>2016</v>
@@ -15232,7 +15232,7 @@
         <v>356</v>
       </c>
       <c r="C453" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D453" s="20">
         <v>2016</v>
@@ -15264,7 +15264,7 @@
         <v>357</v>
       </c>
       <c r="C454" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D454" s="20">
         <v>2016</v>
@@ -15296,7 +15296,7 @@
         <v>358</v>
       </c>
       <c r="C455" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D455" s="20">
         <v>2016</v>
@@ -15328,7 +15328,7 @@
         <v>359</v>
       </c>
       <c r="C456" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D456" s="20">
         <v>2016</v>
@@ -15360,7 +15360,7 @@
         <v>12</v>
       </c>
       <c r="C457" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D457" s="20">
         <v>2016</v>
@@ -15392,7 +15392,7 @@
         <v>361</v>
       </c>
       <c r="C458" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D458" s="20">
         <v>2016</v>
@@ -15424,7 +15424,7 @@
         <v>3</v>
       </c>
       <c r="C459" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D459" s="16">
         <v>2016</v>
@@ -15456,7 +15456,7 @@
         <v>401</v>
       </c>
       <c r="C460" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D460" s="20">
         <v>2016</v>
@@ -15488,7 +15488,7 @@
         <v>13</v>
       </c>
       <c r="C461" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D461" s="20">
         <v>2016</v>
@@ -15520,7 +15520,7 @@
         <v>403</v>
       </c>
       <c r="C462" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D462" s="20">
         <v>2016</v>
@@ -15552,7 +15552,7 @@
         <v>404</v>
       </c>
       <c r="C463" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D463" s="20">
         <v>2016</v>
@@ -15584,7 +15584,7 @@
         <v>405</v>
       </c>
       <c r="C464" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D464" s="20">
         <v>2016</v>
@@ -15616,7 +15616,7 @@
         <v>451</v>
       </c>
       <c r="C465" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D465" s="20">
         <v>2016</v>
@@ -15648,7 +15648,7 @@
         <v>452</v>
       </c>
       <c r="C466" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D466" s="20">
         <v>2016</v>
@@ -15680,7 +15680,7 @@
         <v>453</v>
       </c>
       <c r="C467" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D467" s="20">
         <v>2016</v>
@@ -15712,7 +15712,7 @@
         <v>454</v>
       </c>
       <c r="C468" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D468" s="20">
         <v>2016</v>
@@ -15744,7 +15744,7 @@
         <v>14</v>
       </c>
       <c r="C469" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D469" s="20">
         <v>2016</v>
@@ -15776,7 +15776,7 @@
         <v>456</v>
       </c>
       <c r="C470" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D470" s="20">
         <v>2016</v>
@@ -15808,7 +15808,7 @@
         <v>13</v>
       </c>
       <c r="C471" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D471" s="20">
         <v>2016</v>
@@ -15840,7 +15840,7 @@
         <v>458</v>
       </c>
       <c r="C472" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D472" s="20">
         <v>2016</v>
@@ -15872,7 +15872,7 @@
         <v>459</v>
       </c>
       <c r="C473" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D473" s="20">
         <v>2016</v>
@@ -15904,7 +15904,7 @@
         <v>460</v>
       </c>
       <c r="C474" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D474" s="20">
         <v>2016</v>
@@ -15936,7 +15936,7 @@
         <v>461</v>
       </c>
       <c r="C475" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D475" s="20">
         <v>2016</v>
@@ -15968,7 +15968,7 @@
         <v>14</v>
       </c>
       <c r="C476" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D476" s="20">
         <v>2016</v>
@@ -16000,7 +16000,7 @@
         <v>4</v>
       </c>
       <c r="C477" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D477" s="16">
         <v>2016</v>
@@ -16032,7 +16032,7 @@
         <v>0</v>
       </c>
       <c r="C478" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D478" s="16">
         <v>2016</v>
@@ -16064,7 +16064,7 @@
         <v>101</v>
       </c>
       <c r="C479" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D479" s="20">
         <v>2015</v>
@@ -16096,7 +16096,7 @@
         <v>102</v>
       </c>
       <c r="C480" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D480" s="20">
         <v>2015</v>
@@ -16128,7 +16128,7 @@
         <v>103</v>
       </c>
       <c r="C481" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D481" s="20">
         <v>2015</v>
@@ -16160,7 +16160,7 @@
         <v>151</v>
       </c>
       <c r="C482" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D482" s="20">
         <v>2015</v>
@@ -16192,7 +16192,7 @@
         <v>153</v>
       </c>
       <c r="C483" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D483" s="20">
         <v>2015</v>
@@ -16224,7 +16224,7 @@
         <v>154</v>
       </c>
       <c r="C484" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D484" s="20">
         <v>2015</v>
@@ -16256,7 +16256,7 @@
         <v>155</v>
       </c>
       <c r="C485" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D485" s="20">
         <v>2015</v>
@@ -16288,7 +16288,7 @@
         <v>157</v>
       </c>
       <c r="C486" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D486" s="20">
         <v>2015</v>
@@ -16320,7 +16320,7 @@
         <v>158</v>
       </c>
       <c r="C487" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D487" s="20">
         <v>2015</v>
@@ -16352,7 +16352,7 @@
         <v>159</v>
       </c>
       <c r="C488" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D488" s="20">
         <v>2015</v>
@@ -16384,7 +16384,7 @@
         <v>1</v>
       </c>
       <c r="C489" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D489" s="16">
         <v>2015</v>
@@ -16416,7 +16416,7 @@
         <v>241</v>
       </c>
       <c r="C490" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D490" s="20">
         <v>2015</v>
@@ -16448,7 +16448,7 @@
         <v>241001</v>
       </c>
       <c r="C491" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D491" s="20">
         <v>2015</v>
@@ -16480,7 +16480,7 @@
         <v>241999</v>
       </c>
       <c r="C492" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D492" s="20">
         <v>2015</v>
@@ -16512,7 +16512,7 @@
         <v>251</v>
       </c>
       <c r="C493" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D493" s="20">
         <v>2015</v>
@@ -16544,7 +16544,7 @@
         <v>252</v>
       </c>
       <c r="C494" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D494" s="20">
         <v>2015</v>
@@ -16576,7 +16576,7 @@
         <v>254</v>
       </c>
       <c r="C495" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D495" s="20">
         <v>2015</v>
@@ -16608,7 +16608,7 @@
         <v>255</v>
       </c>
       <c r="C496" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D496" s="20">
         <v>2015</v>
@@ -16640,7 +16640,7 @@
         <v>256</v>
       </c>
       <c r="C497" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D497" s="20">
         <v>2015</v>
@@ -16672,7 +16672,7 @@
         <v>257</v>
       </c>
       <c r="C498" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D498" s="20">
         <v>2015</v>
@@ -16704,7 +16704,7 @@
         <v>2</v>
       </c>
       <c r="C499" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D499" s="16">
         <v>2015</v>
@@ -16736,7 +16736,7 @@
         <v>351</v>
       </c>
       <c r="C500" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D500" s="20">
         <v>2015</v>
@@ -16768,7 +16768,7 @@
         <v>352</v>
       </c>
       <c r="C501" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D501" s="20">
         <v>2015</v>
@@ -16800,7 +16800,7 @@
         <v>353</v>
       </c>
       <c r="C502" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D502" s="20">
         <v>2015</v>
@@ -16832,7 +16832,7 @@
         <v>12</v>
       </c>
       <c r="C503" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D503" s="20">
         <v>2015</v>
@@ -16864,7 +16864,7 @@
         <v>355</v>
       </c>
       <c r="C504" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D504" s="20">
         <v>2015</v>
@@ -16896,7 +16896,7 @@
         <v>356</v>
       </c>
       <c r="C505" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D505" s="20">
         <v>2015</v>
@@ -16928,7 +16928,7 @@
         <v>357</v>
       </c>
       <c r="C506" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D506" s="20">
         <v>2015</v>
@@ -16960,7 +16960,7 @@
         <v>358</v>
       </c>
       <c r="C507" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D507" s="20">
         <v>2015</v>
@@ -16992,7 +16992,7 @@
         <v>359</v>
       </c>
       <c r="C508" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D508" s="20">
         <v>2015</v>
@@ -17024,7 +17024,7 @@
         <v>12</v>
       </c>
       <c r="C509" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D509" s="20">
         <v>2015</v>
@@ -17056,7 +17056,7 @@
         <v>361</v>
       </c>
       <c r="C510" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D510" s="20">
         <v>2015</v>
@@ -17088,7 +17088,7 @@
         <v>3</v>
       </c>
       <c r="C511" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D511" s="16">
         <v>2015</v>
@@ -17120,7 +17120,7 @@
         <v>401</v>
       </c>
       <c r="C512" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D512" s="20">
         <v>2015</v>
@@ -17152,7 +17152,7 @@
         <v>13</v>
       </c>
       <c r="C513" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D513" s="20">
         <v>2015</v>
@@ -17184,7 +17184,7 @@
         <v>403</v>
       </c>
       <c r="C514" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D514" s="20">
         <v>2015</v>
@@ -17216,7 +17216,7 @@
         <v>404</v>
       </c>
       <c r="C515" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D515" s="20">
         <v>2015</v>
@@ -17248,7 +17248,7 @@
         <v>405</v>
       </c>
       <c r="C516" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D516" s="20">
         <v>2015</v>
@@ -17280,7 +17280,7 @@
         <v>451</v>
       </c>
       <c r="C517" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D517" s="20">
         <v>2015</v>
@@ -17312,7 +17312,7 @@
         <v>452</v>
       </c>
       <c r="C518" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D518" s="20">
         <v>2015</v>
@@ -17344,7 +17344,7 @@
         <v>453</v>
       </c>
       <c r="C519" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D519" s="20">
         <v>2015</v>
@@ -17376,7 +17376,7 @@
         <v>454</v>
       </c>
       <c r="C520" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D520" s="20">
         <v>2015</v>
@@ -17408,7 +17408,7 @@
         <v>14</v>
       </c>
       <c r="C521" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D521" s="20">
         <v>2015</v>
@@ -17440,7 +17440,7 @@
         <v>456</v>
       </c>
       <c r="C522" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D522" s="20">
         <v>2015</v>
@@ -17472,7 +17472,7 @@
         <v>13</v>
       </c>
       <c r="C523" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D523" s="20">
         <v>2015</v>
@@ -17504,7 +17504,7 @@
         <v>458</v>
       </c>
       <c r="C524" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D524" s="20">
         <v>2015</v>
@@ -17536,7 +17536,7 @@
         <v>459</v>
       </c>
       <c r="C525" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D525" s="20">
         <v>2015</v>
@@ -17568,7 +17568,7 @@
         <v>460</v>
       </c>
       <c r="C526" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D526" s="20">
         <v>2015</v>
@@ -17600,7 +17600,7 @@
         <v>461</v>
       </c>
       <c r="C527" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D527" s="20">
         <v>2015</v>
@@ -17632,7 +17632,7 @@
         <v>14</v>
       </c>
       <c r="C528" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D528" s="20">
         <v>2015</v>
@@ -17664,7 +17664,7 @@
         <v>4</v>
       </c>
       <c r="C529" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D529" s="16">
         <v>2015</v>
@@ -17696,7 +17696,7 @@
         <v>0</v>
       </c>
       <c r="C530" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D530" s="16">
         <v>2015</v>
@@ -17728,7 +17728,7 @@
         <v>101</v>
       </c>
       <c r="C531" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D531" s="20">
         <v>2014</v>
@@ -17760,7 +17760,7 @@
         <v>102</v>
       </c>
       <c r="C532" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D532" s="20">
         <v>2014</v>
@@ -17792,7 +17792,7 @@
         <v>103</v>
       </c>
       <c r="C533" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D533" s="20">
         <v>2014</v>
@@ -17824,7 +17824,7 @@
         <v>151</v>
       </c>
       <c r="C534" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D534" s="20">
         <v>2014</v>
@@ -17856,7 +17856,7 @@
         <v>153</v>
       </c>
       <c r="C535" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D535" s="20">
         <v>2014</v>
@@ -17888,7 +17888,7 @@
         <v>154</v>
       </c>
       <c r="C536" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D536" s="20">
         <v>2014</v>
@@ -17920,7 +17920,7 @@
         <v>155</v>
       </c>
       <c r="C537" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D537" s="20">
         <v>2014</v>
@@ -17952,7 +17952,7 @@
         <v>157</v>
       </c>
       <c r="C538" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D538" s="20">
         <v>2014</v>
@@ -17984,7 +17984,7 @@
         <v>158</v>
       </c>
       <c r="C539" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D539" s="20">
         <v>2014</v>
@@ -18016,7 +18016,7 @@
         <v>159</v>
       </c>
       <c r="C540" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D540" s="20">
         <v>2014</v>
@@ -18048,7 +18048,7 @@
         <v>1</v>
       </c>
       <c r="C541" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D541" s="16">
         <v>2014</v>
@@ -18080,7 +18080,7 @@
         <v>241</v>
       </c>
       <c r="C542" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D542" s="20">
         <v>2014</v>
@@ -18112,7 +18112,7 @@
         <v>241001</v>
       </c>
       <c r="C543" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D543" s="20">
         <v>2014</v>
@@ -18144,7 +18144,7 @@
         <v>241999</v>
       </c>
       <c r="C544" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D544" s="20">
         <v>2014</v>
@@ -18176,7 +18176,7 @@
         <v>251</v>
       </c>
       <c r="C545" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D545" s="20">
         <v>2014</v>
@@ -18208,7 +18208,7 @@
         <v>252</v>
       </c>
       <c r="C546" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D546" s="20">
         <v>2014</v>
@@ -18240,7 +18240,7 @@
         <v>254</v>
       </c>
       <c r="C547" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D547" s="20">
         <v>2014</v>
@@ -18272,7 +18272,7 @@
         <v>255</v>
       </c>
       <c r="C548" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D548" s="20">
         <v>2014</v>
@@ -18304,7 +18304,7 @@
         <v>256</v>
       </c>
       <c r="C549" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D549" s="20">
         <v>2014</v>
@@ -18336,7 +18336,7 @@
         <v>257</v>
       </c>
       <c r="C550" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D550" s="20">
         <v>2014</v>
@@ -18368,7 +18368,7 @@
         <v>2</v>
       </c>
       <c r="C551" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D551" s="16">
         <v>2014</v>
@@ -18400,7 +18400,7 @@
         <v>351</v>
       </c>
       <c r="C552" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D552" s="20">
         <v>2014</v>
@@ -18432,7 +18432,7 @@
         <v>352</v>
       </c>
       <c r="C553" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D553" s="20">
         <v>2014</v>
@@ -18464,7 +18464,7 @@
         <v>353</v>
       </c>
       <c r="C554" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D554" s="20">
         <v>2014</v>
@@ -18496,7 +18496,7 @@
         <v>12</v>
       </c>
       <c r="C555" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D555" s="20">
         <v>2014</v>
@@ -18528,7 +18528,7 @@
         <v>355</v>
       </c>
       <c r="C556" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D556" s="20">
         <v>2014</v>
@@ -18560,7 +18560,7 @@
         <v>356</v>
       </c>
       <c r="C557" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D557" s="20">
         <v>2014</v>
@@ -18592,7 +18592,7 @@
         <v>357</v>
       </c>
       <c r="C558" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D558" s="20">
         <v>2014</v>
@@ -18624,7 +18624,7 @@
         <v>358</v>
       </c>
       <c r="C559" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D559" s="20">
         <v>2014</v>
@@ -18656,7 +18656,7 @@
         <v>359</v>
       </c>
       <c r="C560" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D560" s="20">
         <v>2014</v>
@@ -18688,7 +18688,7 @@
         <v>12</v>
       </c>
       <c r="C561" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D561" s="20">
         <v>2014</v>
@@ -18720,7 +18720,7 @@
         <v>361</v>
       </c>
       <c r="C562" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D562" s="20">
         <v>2014</v>
@@ -18752,7 +18752,7 @@
         <v>3</v>
       </c>
       <c r="C563" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D563" s="16">
         <v>2014</v>
@@ -18784,7 +18784,7 @@
         <v>401</v>
       </c>
       <c r="C564" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D564" s="20">
         <v>2014</v>
@@ -18816,7 +18816,7 @@
         <v>13</v>
       </c>
       <c r="C565" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D565" s="20">
         <v>2014</v>
@@ -18848,7 +18848,7 @@
         <v>403</v>
       </c>
       <c r="C566" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D566" s="20">
         <v>2014</v>
@@ -18880,7 +18880,7 @@
         <v>404</v>
       </c>
       <c r="C567" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D567" s="20">
         <v>2014</v>
@@ -18912,7 +18912,7 @@
         <v>405</v>
       </c>
       <c r="C568" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D568" s="20">
         <v>2014</v>
@@ -18944,7 +18944,7 @@
         <v>451</v>
       </c>
       <c r="C569" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D569" s="20">
         <v>2014</v>
@@ -18976,7 +18976,7 @@
         <v>452</v>
       </c>
       <c r="C570" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D570" s="20">
         <v>2014</v>
@@ -19008,7 +19008,7 @@
         <v>453</v>
       </c>
       <c r="C571" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D571" s="20">
         <v>2014</v>
@@ -19040,7 +19040,7 @@
         <v>454</v>
       </c>
       <c r="C572" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D572" s="20">
         <v>2014</v>
@@ -19072,7 +19072,7 @@
         <v>14</v>
       </c>
       <c r="C573" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D573" s="20">
         <v>2014</v>
@@ -19104,7 +19104,7 @@
         <v>456</v>
       </c>
       <c r="C574" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D574" s="20">
         <v>2014</v>
@@ -19136,7 +19136,7 @@
         <v>13</v>
       </c>
       <c r="C575" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D575" s="20">
         <v>2014</v>
@@ -19168,7 +19168,7 @@
         <v>458</v>
       </c>
       <c r="C576" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D576" s="20">
         <v>2014</v>
@@ -19200,7 +19200,7 @@
         <v>459</v>
       </c>
       <c r="C577" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D577" s="20">
         <v>2014</v>
@@ -19232,7 +19232,7 @@
         <v>460</v>
       </c>
       <c r="C578" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D578" s="20">
         <v>2014</v>
@@ -19264,7 +19264,7 @@
         <v>461</v>
       </c>
       <c r="C579" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D579" s="20">
         <v>2014</v>
@@ -19296,7 +19296,7 @@
         <v>14</v>
       </c>
       <c r="C580" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D580" s="20">
         <v>2014</v>
@@ -19328,7 +19328,7 @@
         <v>4</v>
       </c>
       <c r="C581" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D581" s="16">
         <v>2014</v>
@@ -19360,7 +19360,7 @@
         <v>0</v>
       </c>
       <c r="C582" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D582" s="16">
         <v>2014</v>
@@ -19392,7 +19392,7 @@
         <v>101</v>
       </c>
       <c r="C583" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D583" s="20">
         <v>2013</v>
@@ -19424,7 +19424,7 @@
         <v>102</v>
       </c>
       <c r="C584" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D584" s="20">
         <v>2013</v>
@@ -19456,7 +19456,7 @@
         <v>103</v>
       </c>
       <c r="C585" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D585" s="20">
         <v>2013</v>
@@ -19488,7 +19488,7 @@
         <v>151</v>
       </c>
       <c r="C586" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D586" s="20">
         <v>2013</v>
@@ -19520,7 +19520,7 @@
         <v>153</v>
       </c>
       <c r="C587" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D587" s="20">
         <v>2013</v>
@@ -19552,7 +19552,7 @@
         <v>154</v>
       </c>
       <c r="C588" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D588" s="20">
         <v>2013</v>
@@ -19584,7 +19584,7 @@
         <v>155</v>
       </c>
       <c r="C589" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D589" s="20">
         <v>2013</v>
@@ -19616,7 +19616,7 @@
         <v>157</v>
       </c>
       <c r="C590" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D590" s="20">
         <v>2013</v>
@@ -19648,7 +19648,7 @@
         <v>158</v>
       </c>
       <c r="C591" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D591" s="20">
         <v>2013</v>
@@ -19680,7 +19680,7 @@
         <v>159</v>
       </c>
       <c r="C592" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D592" s="20">
         <v>2013</v>
@@ -19712,7 +19712,7 @@
         <v>1</v>
       </c>
       <c r="C593" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D593" s="16">
         <v>2013</v>
@@ -19744,7 +19744,7 @@
         <v>241</v>
       </c>
       <c r="C594" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D594" s="20">
         <v>2013</v>
@@ -19776,7 +19776,7 @@
         <v>241001</v>
       </c>
       <c r="C595" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D595" s="20">
         <v>2013</v>
@@ -19808,7 +19808,7 @@
         <v>241999</v>
       </c>
       <c r="C596" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D596" s="20">
         <v>2013</v>
@@ -19840,7 +19840,7 @@
         <v>251</v>
       </c>
       <c r="C597" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D597" s="20">
         <v>2013</v>
@@ -19872,7 +19872,7 @@
         <v>252</v>
       </c>
       <c r="C598" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D598" s="20">
         <v>2013</v>
@@ -19904,7 +19904,7 @@
         <v>254</v>
       </c>
       <c r="C599" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D599" s="20">
         <v>2013</v>
@@ -19936,7 +19936,7 @@
         <v>255</v>
       </c>
       <c r="C600" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D600" s="20">
         <v>2013</v>
@@ -19968,7 +19968,7 @@
         <v>256</v>
       </c>
       <c r="C601" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D601" s="20">
         <v>2013</v>
@@ -20000,7 +20000,7 @@
         <v>257</v>
       </c>
       <c r="C602" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D602" s="20">
         <v>2013</v>
@@ -20032,7 +20032,7 @@
         <v>2</v>
       </c>
       <c r="C603" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D603" s="16">
         <v>2013</v>
@@ -20064,7 +20064,7 @@
         <v>351</v>
       </c>
       <c r="C604" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D604" s="20">
         <v>2013</v>
@@ -20096,7 +20096,7 @@
         <v>352</v>
       </c>
       <c r="C605" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D605" s="20">
         <v>2013</v>
@@ -20128,7 +20128,7 @@
         <v>353</v>
       </c>
       <c r="C606" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D606" s="20">
         <v>2013</v>
@@ -20160,7 +20160,7 @@
         <v>12</v>
       </c>
       <c r="C607" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D607" s="20">
         <v>2013</v>
@@ -20192,7 +20192,7 @@
         <v>355</v>
       </c>
       <c r="C608" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D608" s="20">
         <v>2013</v>
@@ -20224,7 +20224,7 @@
         <v>356</v>
       </c>
       <c r="C609" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D609" s="20">
         <v>2013</v>
@@ -20256,7 +20256,7 @@
         <v>357</v>
       </c>
       <c r="C610" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D610" s="20">
         <v>2013</v>
@@ -20288,7 +20288,7 @@
         <v>358</v>
       </c>
       <c r="C611" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D611" s="20">
         <v>2013</v>
@@ -20320,7 +20320,7 @@
         <v>359</v>
       </c>
       <c r="C612" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D612" s="20">
         <v>2013</v>
@@ -20352,7 +20352,7 @@
         <v>12</v>
       </c>
       <c r="C613" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D613" s="20">
         <v>2013</v>
@@ -20384,7 +20384,7 @@
         <v>361</v>
       </c>
       <c r="C614" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D614" s="20">
         <v>2013</v>
@@ -20416,7 +20416,7 @@
         <v>3</v>
       </c>
       <c r="C615" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D615" s="16">
         <v>2013</v>
@@ -20448,7 +20448,7 @@
         <v>401</v>
       </c>
       <c r="C616" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D616" s="20">
         <v>2013</v>
@@ -20480,7 +20480,7 @@
         <v>13</v>
       </c>
       <c r="C617" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D617" s="20">
         <v>2013</v>
@@ -20512,7 +20512,7 @@
         <v>403</v>
       </c>
       <c r="C618" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D618" s="20">
         <v>2013</v>
@@ -20544,7 +20544,7 @@
         <v>404</v>
       </c>
       <c r="C619" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D619" s="20">
         <v>2013</v>
@@ -20576,7 +20576,7 @@
         <v>405</v>
       </c>
       <c r="C620" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D620" s="20">
         <v>2013</v>
@@ -20608,7 +20608,7 @@
         <v>451</v>
       </c>
       <c r="C621" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D621" s="20">
         <v>2013</v>
@@ -20640,7 +20640,7 @@
         <v>452</v>
       </c>
       <c r="C622" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D622" s="20">
         <v>2013</v>
@@ -20672,7 +20672,7 @@
         <v>453</v>
       </c>
       <c r="C623" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D623" s="20">
         <v>2013</v>
@@ -20704,7 +20704,7 @@
         <v>454</v>
       </c>
       <c r="C624" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D624" s="20">
         <v>2013</v>
@@ -20736,7 +20736,7 @@
         <v>14</v>
       </c>
       <c r="C625" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D625" s="20">
         <v>2013</v>
@@ -20768,7 +20768,7 @@
         <v>456</v>
       </c>
       <c r="C626" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D626" s="20">
         <v>2013</v>
@@ -20800,7 +20800,7 @@
         <v>13</v>
       </c>
       <c r="C627" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D627" s="20">
         <v>2013</v>
@@ -20832,7 +20832,7 @@
         <v>458</v>
       </c>
       <c r="C628" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D628" s="20">
         <v>2013</v>
@@ -20864,7 +20864,7 @@
         <v>459</v>
       </c>
       <c r="C629" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D629" s="20">
         <v>2013</v>
@@ -20896,7 +20896,7 @@
         <v>460</v>
       </c>
       <c r="C630" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D630" s="20">
         <v>2013</v>
@@ -20928,7 +20928,7 @@
         <v>461</v>
       </c>
       <c r="C631" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D631" s="20">
         <v>2013</v>
@@ -20960,7 +20960,7 @@
         <v>14</v>
       </c>
       <c r="C632" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D632" s="20">
         <v>2013</v>
@@ -20992,7 +20992,7 @@
         <v>4</v>
       </c>
       <c r="C633" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D633" s="16">
         <v>2013</v>
@@ -21024,7 +21024,7 @@
         <v>0</v>
       </c>
       <c r="C634" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D634" s="16">
         <v>2013</v>
@@ -21056,7 +21056,7 @@
         <v>101</v>
       </c>
       <c r="C635" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D635" s="20">
         <v>2012</v>
@@ -21088,7 +21088,7 @@
         <v>102</v>
       </c>
       <c r="C636" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D636" s="20">
         <v>2012</v>
@@ -21120,7 +21120,7 @@
         <v>103</v>
       </c>
       <c r="C637" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D637" s="20">
         <v>2012</v>
@@ -21152,7 +21152,7 @@
         <v>151</v>
       </c>
       <c r="C638" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D638" s="20">
         <v>2012</v>
@@ -21184,7 +21184,7 @@
         <v>153</v>
       </c>
       <c r="C639" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D639" s="20">
         <v>2012</v>
@@ -21216,7 +21216,7 @@
         <v>154</v>
       </c>
       <c r="C640" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D640" s="20">
         <v>2012</v>
@@ -21248,7 +21248,7 @@
         <v>155</v>
       </c>
       <c r="C641" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D641" s="20">
         <v>2012</v>
@@ -21280,7 +21280,7 @@
         <v>157</v>
       </c>
       <c r="C642" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D642" s="20">
         <v>2012</v>
@@ -21312,7 +21312,7 @@
         <v>159</v>
       </c>
       <c r="C643" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D643" s="20">
         <v>2012</v>
@@ -21344,7 +21344,7 @@
         <v>158</v>
       </c>
       <c r="C644" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D644" s="20">
         <v>2012</v>
@@ -21376,7 +21376,7 @@
         <v>1</v>
       </c>
       <c r="C645" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D645" s="16">
         <v>2012</v>
@@ -21408,7 +21408,7 @@
         <v>241</v>
       </c>
       <c r="C646" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D646" s="20">
         <v>2012</v>
@@ -21440,7 +21440,7 @@
         <v>241001</v>
       </c>
       <c r="C647" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D647" s="20">
         <v>2012</v>
@@ -21472,7 +21472,7 @@
         <v>241999</v>
       </c>
       <c r="C648" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D648" s="20">
         <v>2012</v>
@@ -21504,7 +21504,7 @@
         <v>251</v>
       </c>
       <c r="C649" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D649" s="20">
         <v>2012</v>
@@ -21536,7 +21536,7 @@
         <v>252</v>
       </c>
       <c r="C650" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D650" s="20">
         <v>2012</v>
@@ -21568,7 +21568,7 @@
         <v>254</v>
       </c>
       <c r="C651" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D651" s="20">
         <v>2012</v>
@@ -21600,7 +21600,7 @@
         <v>255</v>
       </c>
       <c r="C652" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D652" s="20">
         <v>2012</v>
@@ -21632,7 +21632,7 @@
         <v>256</v>
       </c>
       <c r="C653" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D653" s="20">
         <v>2012</v>
@@ -21664,7 +21664,7 @@
         <v>257</v>
       </c>
       <c r="C654" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D654" s="20">
         <v>2012</v>
@@ -21696,7 +21696,7 @@
         <v>2</v>
       </c>
       <c r="C655" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D655" s="16">
         <v>2012</v>
@@ -21728,7 +21728,7 @@
         <v>351</v>
       </c>
       <c r="C656" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D656" s="20">
         <v>2012</v>
@@ -21760,7 +21760,7 @@
         <v>352</v>
       </c>
       <c r="C657" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D657" s="20">
         <v>2012</v>
@@ -21792,7 +21792,7 @@
         <v>353</v>
       </c>
       <c r="C658" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D658" s="20">
         <v>2012</v>
@@ -21824,7 +21824,7 @@
         <v>12</v>
       </c>
       <c r="C659" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D659" s="20">
         <v>2012</v>
@@ -21856,7 +21856,7 @@
         <v>355</v>
       </c>
       <c r="C660" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D660" s="20">
         <v>2012</v>
@@ -21888,7 +21888,7 @@
         <v>356</v>
       </c>
       <c r="C661" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D661" s="20">
         <v>2012</v>
@@ -21920,7 +21920,7 @@
         <v>357</v>
       </c>
       <c r="C662" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D662" s="20">
         <v>2012</v>
@@ -21952,7 +21952,7 @@
         <v>358</v>
       </c>
       <c r="C663" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D663" s="20">
         <v>2012</v>
@@ -21984,7 +21984,7 @@
         <v>359</v>
       </c>
       <c r="C664" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D664" s="20">
         <v>2012</v>
@@ -22016,7 +22016,7 @@
         <v>12</v>
       </c>
       <c r="C665" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D665" s="20">
         <v>2012</v>
@@ -22048,7 +22048,7 @@
         <v>361</v>
       </c>
       <c r="C666" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D666" s="20">
         <v>2012</v>
@@ -22080,7 +22080,7 @@
         <v>3</v>
       </c>
       <c r="C667" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D667" s="16">
         <v>2012</v>
@@ -22112,7 +22112,7 @@
         <v>401</v>
       </c>
       <c r="C668" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D668" s="20">
         <v>2012</v>
@@ -22144,7 +22144,7 @@
         <v>13</v>
       </c>
       <c r="C669" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D669" s="20">
         <v>2012</v>
@@ -22176,7 +22176,7 @@
         <v>403</v>
       </c>
       <c r="C670" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D670" s="20">
         <v>2012</v>
@@ -22208,7 +22208,7 @@
         <v>404</v>
       </c>
       <c r="C671" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D671" s="20">
         <v>2012</v>
@@ -22240,7 +22240,7 @@
         <v>405</v>
       </c>
       <c r="C672" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D672" s="20">
         <v>2012</v>
@@ -22272,7 +22272,7 @@
         <v>451</v>
       </c>
       <c r="C673" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D673" s="20">
         <v>2012</v>
@@ -22304,7 +22304,7 @@
         <v>452</v>
       </c>
       <c r="C674" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D674" s="20">
         <v>2012</v>
@@ -22336,7 +22336,7 @@
         <v>453</v>
       </c>
       <c r="C675" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D675" s="20">
         <v>2012</v>
@@ -22368,7 +22368,7 @@
         <v>454</v>
       </c>
       <c r="C676" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D676" s="20">
         <v>2012</v>
@@ -22400,7 +22400,7 @@
         <v>14</v>
       </c>
       <c r="C677" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D677" s="20">
         <v>2012</v>
@@ -22432,7 +22432,7 @@
         <v>456</v>
       </c>
       <c r="C678" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D678" s="20">
         <v>2012</v>
@@ -22464,7 +22464,7 @@
         <v>13</v>
       </c>
       <c r="C679" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D679" s="20">
         <v>2012</v>
@@ -22496,7 +22496,7 @@
         <v>458</v>
       </c>
       <c r="C680" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D680" s="20">
         <v>2012</v>
@@ -22528,7 +22528,7 @@
         <v>459</v>
       </c>
       <c r="C681" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D681" s="20">
         <v>2012</v>
@@ -22560,7 +22560,7 @@
         <v>460</v>
       </c>
       <c r="C682" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D682" s="20">
         <v>2012</v>
@@ -22592,7 +22592,7 @@
         <v>461</v>
       </c>
       <c r="C683" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D683" s="20">
         <v>2012</v>
@@ -22624,7 +22624,7 @@
         <v>14</v>
       </c>
       <c r="C684" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D684" s="20">
         <v>2012</v>
@@ -22656,7 +22656,7 @@
         <v>4</v>
       </c>
       <c r="C685" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D685" s="16">
         <v>2012</v>
@@ -22688,7 +22688,7 @@
         <v>0</v>
       </c>
       <c r="C686" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D686" s="16">
         <v>2012</v>
@@ -22720,7 +22720,7 @@
         <v>101</v>
       </c>
       <c r="C687" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D687" s="19">
         <v>2011</v>
@@ -22753,7 +22753,7 @@
         <v>102</v>
       </c>
       <c r="C688" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D688" s="30">
         <v>2011</v>
@@ -22785,7 +22785,7 @@
         <v>103</v>
       </c>
       <c r="C689" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D689" s="30">
         <v>2011</v>
@@ -22818,7 +22818,7 @@
         <v>151</v>
       </c>
       <c r="C690" s="31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D690" s="31">
         <v>2011</v>
@@ -22851,7 +22851,7 @@
         <v>153</v>
       </c>
       <c r="C691" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D691" s="32">
         <v>2011</v>
@@ -22884,7 +22884,7 @@
         <v>154</v>
       </c>
       <c r="C692" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D692" s="25">
         <v>2011</v>
@@ -22916,7 +22916,7 @@
         <v>155</v>
       </c>
       <c r="C693" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D693" s="19">
         <v>2011</v>
@@ -22948,7 +22948,7 @@
         <v>157</v>
       </c>
       <c r="C694" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D694" s="19">
         <v>2011</v>
@@ -22980,7 +22980,7 @@
         <v>158</v>
       </c>
       <c r="C695" s="28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D695" s="19">
         <v>2011</v>
@@ -23012,7 +23012,7 @@
         <v>159</v>
       </c>
       <c r="C696" s="28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D696" s="19">
         <v>2011</v>
@@ -23044,7 +23044,7 @@
         <v>1</v>
       </c>
       <c r="C697" s="29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D697" s="19">
         <v>2011</v>
@@ -23076,7 +23076,7 @@
         <v>241</v>
       </c>
       <c r="C698" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D698" s="19">
         <v>2011</v>
@@ -23108,7 +23108,7 @@
         <v>241001</v>
       </c>
       <c r="C699" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D699" s="19">
         <v>2011</v>
@@ -23140,7 +23140,7 @@
         <v>241999</v>
       </c>
       <c r="C700" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D700" s="19">
         <v>2011</v>
@@ -23172,7 +23172,7 @@
         <v>251</v>
       </c>
       <c r="C701" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D701" s="19">
         <v>2011</v>
@@ -23204,7 +23204,7 @@
         <v>252</v>
       </c>
       <c r="C702" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D702" s="19">
         <v>2011</v>
@@ -23236,7 +23236,7 @@
         <v>254</v>
       </c>
       <c r="C703" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D703" s="19">
         <v>2011</v>
@@ -23268,7 +23268,7 @@
         <v>255</v>
       </c>
       <c r="C704" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D704" s="19">
         <v>2011</v>
@@ -23300,7 +23300,7 @@
         <v>256</v>
       </c>
       <c r="C705" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D705" s="19">
         <v>2011</v>
@@ -23332,7 +23332,7 @@
         <v>257</v>
       </c>
       <c r="C706" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D706" s="19">
         <v>2011</v>
@@ -23364,7 +23364,7 @@
         <v>2</v>
       </c>
       <c r="C707" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D707" s="19">
         <v>2011</v>
@@ -23396,7 +23396,7 @@
         <v>351</v>
       </c>
       <c r="C708" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D708" s="19">
         <v>2011</v>
@@ -23428,7 +23428,7 @@
         <v>352</v>
       </c>
       <c r="C709" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D709" s="19">
         <v>2011</v>
@@ -23460,7 +23460,7 @@
         <v>353</v>
       </c>
       <c r="C710" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D710" s="19">
         <v>2011</v>
@@ -23492,7 +23492,7 @@
         <v>12</v>
       </c>
       <c r="C711" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D711" s="19">
         <v>2011</v>
@@ -23524,7 +23524,7 @@
         <v>355</v>
       </c>
       <c r="C712" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D712" s="19">
         <v>2011</v>
@@ -23556,7 +23556,7 @@
         <v>356</v>
       </c>
       <c r="C713" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D713" s="19">
         <v>2011</v>
@@ -23588,7 +23588,7 @@
         <v>357</v>
       </c>
       <c r="C714" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D714" s="19">
         <v>2011</v>
@@ -23620,7 +23620,7 @@
         <v>358</v>
       </c>
       <c r="C715" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D715" s="19">
         <v>2011</v>
@@ -23652,7 +23652,7 @@
         <v>359</v>
       </c>
       <c r="C716" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D716" s="19">
         <v>2011</v>
@@ -23684,7 +23684,7 @@
         <v>12</v>
       </c>
       <c r="C717" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D717" s="19">
         <v>2011</v>
@@ -23716,7 +23716,7 @@
         <v>361</v>
       </c>
       <c r="C718" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D718" s="19">
         <v>2011</v>
@@ -23748,7 +23748,7 @@
         <v>3</v>
       </c>
       <c r="C719" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D719" s="19">
         <v>2011</v>
@@ -23780,7 +23780,7 @@
         <v>401</v>
       </c>
       <c r="C720" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D720" s="19">
         <v>2011</v>
@@ -23812,7 +23812,7 @@
         <v>13</v>
       </c>
       <c r="C721" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D721" s="19">
         <v>2011</v>
@@ -23844,7 +23844,7 @@
         <v>403</v>
       </c>
       <c r="C722" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D722" s="19">
         <v>2011</v>
@@ -23876,7 +23876,7 @@
         <v>404</v>
       </c>
       <c r="C723" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D723" s="19">
         <v>2011</v>
@@ -23908,7 +23908,7 @@
         <v>405</v>
       </c>
       <c r="C724" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D724" s="19">
         <v>2011</v>
@@ -23940,7 +23940,7 @@
         <v>451</v>
       </c>
       <c r="C725" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D725" s="19">
         <v>2011</v>
@@ -23972,7 +23972,7 @@
         <v>452</v>
       </c>
       <c r="C726" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D726" s="19">
         <v>2011</v>
@@ -24004,7 +24004,7 @@
         <v>453</v>
       </c>
       <c r="C727" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D727" s="19">
         <v>2011</v>
@@ -24036,7 +24036,7 @@
         <v>454</v>
       </c>
       <c r="C728" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D728" s="19">
         <v>2011</v>
@@ -24068,7 +24068,7 @@
         <v>14</v>
       </c>
       <c r="C729" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D729" s="19">
         <v>2011</v>
@@ -24100,7 +24100,7 @@
         <v>456</v>
       </c>
       <c r="C730" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D730" s="19">
         <v>2011</v>
@@ -24132,7 +24132,7 @@
         <v>13</v>
       </c>
       <c r="C731" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D731" s="19">
         <v>2011</v>
@@ -24164,7 +24164,7 @@
         <v>458</v>
       </c>
       <c r="C732" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D732" s="19">
         <v>2011</v>
@@ -24196,7 +24196,7 @@
         <v>459</v>
       </c>
       <c r="C733" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D733" s="19">
         <v>2011</v>
@@ -24228,7 +24228,7 @@
         <v>460</v>
       </c>
       <c r="C734" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D734" s="19">
         <v>2011</v>
@@ -24260,7 +24260,7 @@
         <v>461</v>
       </c>
       <c r="C735" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D735" s="19">
         <v>2011</v>
@@ -24292,7 +24292,7 @@
         <v>14</v>
       </c>
       <c r="C736" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D736" s="19">
         <v>2011</v>
@@ -24324,7 +24324,7 @@
         <v>4</v>
       </c>
       <c r="C737" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D737" s="19">
         <v>2011</v>
@@ -24356,7 +24356,7 @@
         <v>0</v>
       </c>
       <c r="C738" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D738" s="19">
         <v>2011</v>
@@ -24415,17 +24415,17 @@
     </row>
     <row r="747" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C747" s="19" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
     </row>
     <row r="748" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C748" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="749" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C749" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/assets/excel/2026_1-3-1.xlsx
+++ b/assets/excel/2026_1-3-1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Hannover\Dez15_Uebergreifende_Analysen\Projekte\Integrationsmonitoring\Schlesier\MT_Site\assets\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C8379D6-9609-4E60-ACC6-86E87C66B939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F1BBE5-00EF-4510-9587-581AF3ABD2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{D0D36073-601B-4828-907B-11F573759D0C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{D0D36073-601B-4828-907B-11F573759D0C}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -119,9 +119,6 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>1) Hochrechnung anhand der Bevölkerungsfortschreibung auf Basis des Zensus 2011. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe. Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren.</t>
   </si>
   <si>
     <t>https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Haushalte-Familien/Methoden/mikrozensus-2020.html</t>
@@ -296,6 +293,9 @@
   </si>
   <si>
     <t>© Landesamt für Statistik Niedersachsen, Hannover 2026,</t>
+  </si>
+  <si>
+    <t>1)  Ab der Veröffentlichung der Endergebnisse 2023 und der Erstergebnisse 2024 werden für die Hochrechnung des Mikrozensus Daten der Bevölkerungsfortschreibung herangezogen, die auf den Eckwerten des Zensus 2022 basieren. Die Hochrechnung für die Jahre vor 2011 sowie für bislang veröffentlichte Ergebnisse des Mikrozensus 2011-2013 basiert auf den fortgeschriebenen Ergebnissen der Volkszählung 1987. In 2016 erfolgte die Umstellung auf eine neue Mikrozensus-Stichprobe (auf Basis des Zensus 2011). Ab 2017 wird nur noch die Bevölkerung in Privathaushalten (ohne Gemeinschaftsunterkünfte) ausgewiesen. Dadurch ergibt sich jeweils eine eingeschränkte Vergleichbarkeit mit den Vorjahren.</t>
   </si>
 </sst>
 </file>
@@ -509,7 +509,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -579,12 +579,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -623,6 +617,9 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -643,9 +640,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -683,7 +680,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -789,7 +786,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -931,7 +928,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -940,7 +937,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22E96BA6-A2BD-4654-9F1D-B326B6986716}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="B1:K749"/>
+  <dimension ref="B1:N749"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="19" customWidth="1"/>
@@ -954,7 +951,7 @@
   <sheetData>
     <row r="1" spans="2:11" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C1" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="2:11" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -976,10 +973,10 @@
     </row>
     <row r="5" spans="2:11" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:11" s="1" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="31" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="7" t="s">
@@ -1005,19 +1002,19 @@
       </c>
     </row>
     <row r="7" spans="2:11" s="1" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="32"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="35">
+      <c r="C7" s="30"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="33">
         <v>1000</v>
       </c>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="38" t="s">
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
     </row>
     <row r="8" spans="2:11" s="1" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="10">
@@ -1053,7 +1050,7 @@
         <v>101</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="12">
         <v>2025</v>
@@ -1085,7 +1082,7 @@
         <v>102</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="12">
         <v>2025</v>
@@ -1117,7 +1114,7 @@
         <v>103</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="12">
         <v>2025</v>
@@ -1149,7 +1146,7 @@
         <v>151</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="12">
         <v>2025</v>
@@ -1181,7 +1178,7 @@
         <v>153</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="12">
         <v>2025</v>
@@ -1213,7 +1210,7 @@
         <v>154</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" s="12">
         <v>2025</v>
@@ -1245,7 +1242,7 @@
         <v>155</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="12">
         <v>2025</v>
@@ -1277,7 +1274,7 @@
         <v>157</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="12">
         <v>2025</v>
@@ -1309,7 +1306,7 @@
         <v>158</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" s="12">
         <v>2025</v>
@@ -1341,7 +1338,7 @@
         <v>159</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D18" s="12">
         <v>2025</v>
@@ -1373,7 +1370,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="16">
         <v>2025</v>
@@ -1405,7 +1402,7 @@
         <v>241</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" s="12">
         <v>2025</v>
@@ -1437,7 +1434,7 @@
         <v>241001</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" s="12">
         <v>2025</v>
@@ -1469,7 +1466,7 @@
         <v>241999</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D22" s="12">
         <v>2025</v>
@@ -1501,7 +1498,7 @@
         <v>251</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D23" s="12">
         <v>2025</v>
@@ -1533,7 +1530,7 @@
         <v>252</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D24" s="12">
         <v>2025</v>
@@ -1565,7 +1562,7 @@
         <v>254</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D25" s="12">
         <v>2025</v>
@@ -1597,7 +1594,7 @@
         <v>255</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" s="12">
         <v>2025</v>
@@ -1629,7 +1626,7 @@
         <v>256</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D27" s="12">
         <v>2025</v>
@@ -1661,7 +1658,7 @@
         <v>257</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D28" s="12">
         <v>2025</v>
@@ -1693,7 +1690,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D29" s="16">
         <v>2025</v>
@@ -1725,7 +1722,7 @@
         <v>351</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D30" s="12">
         <v>2025</v>
@@ -1757,7 +1754,7 @@
         <v>352</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D31" s="12">
         <v>2025</v>
@@ -1789,7 +1786,7 @@
         <v>353</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D32" s="12">
         <v>2025</v>
@@ -1821,7 +1818,7 @@
         <v>12</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33" s="12">
         <v>2025</v>
@@ -1853,7 +1850,7 @@
         <v>355</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D34" s="12">
         <v>2025</v>
@@ -1885,7 +1882,7 @@
         <v>356</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D35" s="12">
         <v>2025</v>
@@ -1917,7 +1914,7 @@
         <v>357</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D36" s="12">
         <v>2025</v>
@@ -1949,7 +1946,7 @@
         <v>358</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D37" s="12">
         <v>2025</v>
@@ -1981,7 +1978,7 @@
         <v>359</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D38" s="12">
         <v>2025</v>
@@ -2013,7 +2010,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D39" s="12">
         <v>2025</v>
@@ -2045,7 +2042,7 @@
         <v>361</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D40" s="12">
         <v>2025</v>
@@ -2077,7 +2074,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D41" s="16">
         <v>2025</v>
@@ -2109,7 +2106,7 @@
         <v>401</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D42" s="12">
         <v>2025</v>
@@ -2141,7 +2138,7 @@
         <v>13</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D43" s="12">
         <v>2025</v>
@@ -2173,7 +2170,7 @@
         <v>403</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D44" s="12">
         <v>2025</v>
@@ -2205,7 +2202,7 @@
         <v>404</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D45" s="12">
         <v>2025</v>
@@ -2237,7 +2234,7 @@
         <v>405</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D46" s="12">
         <v>2025</v>
@@ -2269,7 +2266,7 @@
         <v>451</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D47" s="12">
         <v>2025</v>
@@ -2301,7 +2298,7 @@
         <v>452</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D48" s="12">
         <v>2025</v>
@@ -2333,7 +2330,7 @@
         <v>453</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D49" s="12">
         <v>2025</v>
@@ -2365,7 +2362,7 @@
         <v>454</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D50" s="12">
         <v>2025</v>
@@ -2397,7 +2394,7 @@
         <v>14</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D51" s="12">
         <v>2025</v>
@@ -2429,7 +2426,7 @@
         <v>456</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D52" s="12">
         <v>2025</v>
@@ -2461,7 +2458,7 @@
         <v>13</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D53" s="12">
         <v>2025</v>
@@ -2493,7 +2490,7 @@
         <v>458</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D54" s="12">
         <v>2025</v>
@@ -2525,7 +2522,7 @@
         <v>459</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D55" s="12">
         <v>2025</v>
@@ -2557,7 +2554,7 @@
         <v>460</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D56" s="12">
         <v>2025</v>
@@ -2589,7 +2586,7 @@
         <v>461</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D57" s="12">
         <v>2025</v>
@@ -2621,7 +2618,7 @@
         <v>14</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D58" s="12">
         <v>2025</v>
@@ -2653,7 +2650,7 @@
         <v>4</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D59" s="16">
         <v>2025</v>
@@ -2685,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D60" s="16">
         <v>2025</v>
@@ -2717,7 +2714,7 @@
         <v>101</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D61" s="12">
         <v>2024</v>
@@ -2749,7 +2746,7 @@
         <v>102</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D62" s="12">
         <v>2024</v>
@@ -2781,7 +2778,7 @@
         <v>103</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D63" s="12">
         <v>2024</v>
@@ -2813,7 +2810,7 @@
         <v>151</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D64" s="12">
         <v>2024</v>
@@ -2845,7 +2842,7 @@
         <v>153</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D65" s="12">
         <v>2024</v>
@@ -2877,7 +2874,7 @@
         <v>154</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D66" s="12">
         <v>2024</v>
@@ -2909,7 +2906,7 @@
         <v>155</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D67" s="12">
         <v>2024</v>
@@ -2941,7 +2938,7 @@
         <v>157</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D68" s="12">
         <v>2024</v>
@@ -2973,7 +2970,7 @@
         <v>158</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D69" s="12">
         <v>2024</v>
@@ -3005,7 +3002,7 @@
         <v>159</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D70" s="12">
         <v>2024</v>
@@ -3037,7 +3034,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D71" s="16">
         <v>2024</v>
@@ -3069,7 +3066,7 @@
         <v>241</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D72" s="12">
         <v>2024</v>
@@ -3101,7 +3098,7 @@
         <v>241001</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D73" s="12">
         <v>2024</v>
@@ -3133,7 +3130,7 @@
         <v>241999</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D74" s="12">
         <v>2024</v>
@@ -3165,7 +3162,7 @@
         <v>251</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D75" s="12">
         <v>2024</v>
@@ -3197,7 +3194,7 @@
         <v>252</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D76" s="12">
         <v>2024</v>
@@ -3229,7 +3226,7 @@
         <v>254</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D77" s="12">
         <v>2024</v>
@@ -3261,7 +3258,7 @@
         <v>255</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D78" s="12">
         <v>2024</v>
@@ -3293,7 +3290,7 @@
         <v>256</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D79" s="12">
         <v>2024</v>
@@ -3325,7 +3322,7 @@
         <v>257</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D80" s="12">
         <v>2024</v>
@@ -3357,7 +3354,7 @@
         <v>2</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D81" s="16">
         <v>2024</v>
@@ -3389,7 +3386,7 @@
         <v>351</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D82" s="12">
         <v>2024</v>
@@ -3421,7 +3418,7 @@
         <v>352</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D83" s="12">
         <v>2024</v>
@@ -3453,7 +3450,7 @@
         <v>353</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D84" s="12">
         <v>2024</v>
@@ -3485,7 +3482,7 @@
         <v>12</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D85" s="12">
         <v>2024</v>
@@ -3517,7 +3514,7 @@
         <v>355</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D86" s="12">
         <v>2024</v>
@@ -3549,7 +3546,7 @@
         <v>356</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D87" s="12">
         <v>2024</v>
@@ -3581,7 +3578,7 @@
         <v>357</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D88" s="12">
         <v>2024</v>
@@ -3613,7 +3610,7 @@
         <v>358</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D89" s="12">
         <v>2024</v>
@@ -3645,7 +3642,7 @@
         <v>359</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D90" s="12">
         <v>2024</v>
@@ -3677,7 +3674,7 @@
         <v>12</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D91" s="12">
         <v>2024</v>
@@ -3709,7 +3706,7 @@
         <v>361</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D92" s="12">
         <v>2024</v>
@@ -3741,7 +3738,7 @@
         <v>3</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D93" s="16">
         <v>2024</v>
@@ -3773,7 +3770,7 @@
         <v>401</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D94" s="12">
         <v>2024</v>
@@ -3805,7 +3802,7 @@
         <v>13</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D95" s="12">
         <v>2024</v>
@@ -3837,7 +3834,7 @@
         <v>403</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D96" s="12">
         <v>2024</v>
@@ -3869,7 +3866,7 @@
         <v>404</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D97" s="12">
         <v>2024</v>
@@ -3901,7 +3898,7 @@
         <v>405</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D98" s="12">
         <v>2024</v>
@@ -3933,7 +3930,7 @@
         <v>451</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D99" s="12">
         <v>2024</v>
@@ -3965,7 +3962,7 @@
         <v>452</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D100" s="12">
         <v>2024</v>
@@ -3997,7 +3994,7 @@
         <v>453</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D101" s="12">
         <v>2024</v>
@@ -4029,7 +4026,7 @@
         <v>454</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D102" s="12">
         <v>2024</v>
@@ -4061,7 +4058,7 @@
         <v>14</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D103" s="12">
         <v>2024</v>
@@ -4093,7 +4090,7 @@
         <v>456</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D104" s="12">
         <v>2024</v>
@@ -4125,7 +4122,7 @@
         <v>13</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D105" s="12">
         <v>2024</v>
@@ -4157,7 +4154,7 @@
         <v>458</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D106" s="12">
         <v>2024</v>
@@ -4189,7 +4186,7 @@
         <v>459</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D107" s="12">
         <v>2024</v>
@@ -4221,7 +4218,7 @@
         <v>460</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D108" s="12">
         <v>2024</v>
@@ -4253,7 +4250,7 @@
         <v>461</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D109" s="12">
         <v>2024</v>
@@ -4285,7 +4282,7 @@
         <v>14</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D110" s="12">
         <v>2024</v>
@@ -4317,7 +4314,7 @@
         <v>4</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D111" s="16">
         <v>2024</v>
@@ -4349,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D112" s="16">
         <v>2024</v>
@@ -4381,7 +4378,7 @@
         <v>101</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D113" s="12">
         <v>2023</v>
@@ -4413,7 +4410,7 @@
         <v>102</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D114" s="12">
         <v>2023</v>
@@ -4445,7 +4442,7 @@
         <v>103</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D115" s="12">
         <v>2023</v>
@@ -4477,7 +4474,7 @@
         <v>151</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D116" s="12">
         <v>2023</v>
@@ -4509,7 +4506,7 @@
         <v>153</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D117" s="12">
         <v>2023</v>
@@ -4541,7 +4538,7 @@
         <v>154</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D118" s="12">
         <v>2023</v>
@@ -4573,7 +4570,7 @@
         <v>155</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D119" s="12">
         <v>2023</v>
@@ -4605,7 +4602,7 @@
         <v>157</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D120" s="12">
         <v>2023</v>
@@ -4637,7 +4634,7 @@
         <v>158</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D121" s="12">
         <v>2023</v>
@@ -4669,7 +4666,7 @@
         <v>159</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D122" s="12">
         <v>2023</v>
@@ -4701,7 +4698,7 @@
         <v>1</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D123" s="16">
         <v>2023</v>
@@ -4733,7 +4730,7 @@
         <v>241</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D124" s="12">
         <v>2023</v>
@@ -4765,7 +4762,7 @@
         <v>241001</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D125" s="12">
         <v>2023</v>
@@ -4797,7 +4794,7 @@
         <v>241999</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D126" s="12">
         <v>2023</v>
@@ -4829,7 +4826,7 @@
         <v>251</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D127" s="12">
         <v>2023</v>
@@ -4861,7 +4858,7 @@
         <v>252</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D128" s="12">
         <v>2023</v>
@@ -4893,7 +4890,7 @@
         <v>254</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D129" s="12">
         <v>2023</v>
@@ -4925,7 +4922,7 @@
         <v>255</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D130" s="12">
         <v>2023</v>
@@ -4957,7 +4954,7 @@
         <v>256</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D131" s="12">
         <v>2023</v>
@@ -4989,7 +4986,7 @@
         <v>257</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D132" s="12">
         <v>2023</v>
@@ -5021,7 +5018,7 @@
         <v>2</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D133" s="16">
         <v>2023</v>
@@ -5053,7 +5050,7 @@
         <v>351</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D134" s="12">
         <v>2023</v>
@@ -5085,7 +5082,7 @@
         <v>352</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D135" s="12">
         <v>2023</v>
@@ -5117,7 +5114,7 @@
         <v>353</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D136" s="12">
         <v>2023</v>
@@ -5149,7 +5146,7 @@
         <v>12</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D137" s="12">
         <v>2023</v>
@@ -5181,7 +5178,7 @@
         <v>355</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D138" s="12">
         <v>2023</v>
@@ -5213,7 +5210,7 @@
         <v>356</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D139" s="12">
         <v>2023</v>
@@ -5245,7 +5242,7 @@
         <v>357</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D140" s="12">
         <v>2023</v>
@@ -5277,7 +5274,7 @@
         <v>358</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D141" s="12">
         <v>2023</v>
@@ -5309,7 +5306,7 @@
         <v>359</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D142" s="12">
         <v>2023</v>
@@ -5341,7 +5338,7 @@
         <v>12</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D143" s="12">
         <v>2023</v>
@@ -5373,7 +5370,7 @@
         <v>361</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D144" s="12">
         <v>2023</v>
@@ -5405,7 +5402,7 @@
         <v>3</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D145" s="16">
         <v>2023</v>
@@ -5437,7 +5434,7 @@
         <v>401</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D146" s="12">
         <v>2023</v>
@@ -5469,7 +5466,7 @@
         <v>13</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D147" s="12">
         <v>2023</v>
@@ -5501,7 +5498,7 @@
         <v>403</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D148" s="12">
         <v>2023</v>
@@ -5533,7 +5530,7 @@
         <v>404</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D149" s="12">
         <v>2023</v>
@@ -5565,7 +5562,7 @@
         <v>405</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D150" s="12">
         <v>2023</v>
@@ -5597,7 +5594,7 @@
         <v>451</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D151" s="12">
         <v>2023</v>
@@ -5629,7 +5626,7 @@
         <v>452</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D152" s="12">
         <v>2023</v>
@@ -5661,7 +5658,7 @@
         <v>453</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D153" s="12">
         <v>2023</v>
@@ -5693,7 +5690,7 @@
         <v>454</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D154" s="12">
         <v>2023</v>
@@ -5725,7 +5722,7 @@
         <v>14</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D155" s="12">
         <v>2023</v>
@@ -5757,7 +5754,7 @@
         <v>456</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D156" s="12">
         <v>2023</v>
@@ -5789,7 +5786,7 @@
         <v>13</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D157" s="12">
         <v>2023</v>
@@ -5821,7 +5818,7 @@
         <v>458</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D158" s="12">
         <v>2023</v>
@@ -5853,7 +5850,7 @@
         <v>459</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D159" s="12">
         <v>2023</v>
@@ -5885,7 +5882,7 @@
         <v>460</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D160" s="12">
         <v>2023</v>
@@ -5917,7 +5914,7 @@
         <v>461</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D161" s="12">
         <v>2023</v>
@@ -5949,7 +5946,7 @@
         <v>14</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D162" s="12">
         <v>2023</v>
@@ -5981,7 +5978,7 @@
         <v>4</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D163" s="16">
         <v>2023</v>
@@ -6013,7 +6010,7 @@
         <v>0</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D164" s="16">
         <v>2023</v>
@@ -6045,7 +6042,7 @@
         <v>101</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D165" s="12">
         <v>2022</v>
@@ -6077,7 +6074,7 @@
         <v>102</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D166" s="12">
         <v>2022</v>
@@ -6109,7 +6106,7 @@
         <v>103</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D167" s="12">
         <v>2022</v>
@@ -6141,7 +6138,7 @@
         <v>151</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D168" s="12">
         <v>2022</v>
@@ -6173,7 +6170,7 @@
         <v>153</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D169" s="12">
         <v>2022</v>
@@ -6205,7 +6202,7 @@
         <v>154</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D170" s="12">
         <v>2022</v>
@@ -6237,7 +6234,7 @@
         <v>155</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D171" s="12">
         <v>2022</v>
@@ -6269,7 +6266,7 @@
         <v>157</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D172" s="12">
         <v>2022</v>
@@ -6301,7 +6298,7 @@
         <v>158</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D173" s="12">
         <v>2022</v>
@@ -6333,7 +6330,7 @@
         <v>159</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D174" s="12">
         <v>2022</v>
@@ -6365,7 +6362,7 @@
         <v>1</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D175" s="16">
         <v>2022</v>
@@ -6397,7 +6394,7 @@
         <v>241</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D176" s="12">
         <v>2022</v>
@@ -6429,7 +6426,7 @@
         <v>241001</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D177" s="12">
         <v>2022</v>
@@ -6461,7 +6458,7 @@
         <v>241999</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D178" s="12">
         <v>2022</v>
@@ -6493,7 +6490,7 @@
         <v>251</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D179" s="12">
         <v>2022</v>
@@ -6525,7 +6522,7 @@
         <v>252</v>
       </c>
       <c r="C180" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D180" s="12">
         <v>2022</v>
@@ -6557,7 +6554,7 @@
         <v>254</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D181" s="12">
         <v>2022</v>
@@ -6589,7 +6586,7 @@
         <v>255</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D182" s="12">
         <v>2022</v>
@@ -6621,7 +6618,7 @@
         <v>256</v>
       </c>
       <c r="C183" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D183" s="12">
         <v>2022</v>
@@ -6653,7 +6650,7 @@
         <v>257</v>
       </c>
       <c r="C184" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D184" s="12">
         <v>2022</v>
@@ -6685,7 +6682,7 @@
         <v>2</v>
       </c>
       <c r="C185" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D185" s="16">
         <v>2022</v>
@@ -6717,7 +6714,7 @@
         <v>351</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D186" s="12">
         <v>2022</v>
@@ -6749,7 +6746,7 @@
         <v>352</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D187" s="12">
         <v>2022</v>
@@ -6781,7 +6778,7 @@
         <v>353</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D188" s="12">
         <v>2022</v>
@@ -6813,7 +6810,7 @@
         <v>12</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D189" s="12">
         <v>2022</v>
@@ -6845,7 +6842,7 @@
         <v>355</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D190" s="12">
         <v>2022</v>
@@ -6877,7 +6874,7 @@
         <v>356</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D191" s="12">
         <v>2022</v>
@@ -6909,7 +6906,7 @@
         <v>357</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D192" s="12">
         <v>2022</v>
@@ -6941,7 +6938,7 @@
         <v>358</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D193" s="12">
         <v>2022</v>
@@ -6973,7 +6970,7 @@
         <v>359</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D194" s="12">
         <v>2022</v>
@@ -7005,7 +7002,7 @@
         <v>12</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D195" s="12">
         <v>2022</v>
@@ -7037,7 +7034,7 @@
         <v>361</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D196" s="12">
         <v>2022</v>
@@ -7069,7 +7066,7 @@
         <v>3</v>
       </c>
       <c r="C197" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D197" s="16">
         <v>2022</v>
@@ -7101,7 +7098,7 @@
         <v>401</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D198" s="12">
         <v>2022</v>
@@ -7133,7 +7130,7 @@
         <v>13</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D199" s="12">
         <v>2022</v>
@@ -7165,7 +7162,7 @@
         <v>403</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D200" s="12">
         <v>2022</v>
@@ -7197,7 +7194,7 @@
         <v>404</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D201" s="12">
         <v>2022</v>
@@ -7229,7 +7226,7 @@
         <v>405</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D202" s="12">
         <v>2022</v>
@@ -7261,7 +7258,7 @@
         <v>451</v>
       </c>
       <c r="C203" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D203" s="12">
         <v>2022</v>
@@ -7293,7 +7290,7 @@
         <v>452</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D204" s="12">
         <v>2022</v>
@@ -7325,7 +7322,7 @@
         <v>453</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D205" s="12">
         <v>2022</v>
@@ -7357,7 +7354,7 @@
         <v>454</v>
       </c>
       <c r="C206" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D206" s="12">
         <v>2022</v>
@@ -7389,7 +7386,7 @@
         <v>14</v>
       </c>
       <c r="C207" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D207" s="12">
         <v>2022</v>
@@ -7421,7 +7418,7 @@
         <v>456</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D208" s="12">
         <v>2022</v>
@@ -7453,7 +7450,7 @@
         <v>13</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D209" s="12">
         <v>2022</v>
@@ -7485,7 +7482,7 @@
         <v>458</v>
       </c>
       <c r="C210" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D210" s="12">
         <v>2022</v>
@@ -7517,7 +7514,7 @@
         <v>459</v>
       </c>
       <c r="C211" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D211" s="12">
         <v>2022</v>
@@ -7549,7 +7546,7 @@
         <v>460</v>
       </c>
       <c r="C212" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D212" s="12">
         <v>2022</v>
@@ -7581,7 +7578,7 @@
         <v>461</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D213" s="12">
         <v>2022</v>
@@ -7613,7 +7610,7 @@
         <v>14</v>
       </c>
       <c r="C214" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D214" s="12">
         <v>2022</v>
@@ -7645,7 +7642,7 @@
         <v>4</v>
       </c>
       <c r="C215" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D215" s="16">
         <v>2022</v>
@@ -7677,7 +7674,7 @@
         <v>0</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D216" s="16">
         <v>2022</v>
@@ -7709,7 +7706,7 @@
         <v>101</v>
       </c>
       <c r="C217" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D217" s="16">
         <v>2021</v>
@@ -7741,7 +7738,7 @@
         <v>102</v>
       </c>
       <c r="C218" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D218" s="20">
         <v>2021</v>
@@ -7773,7 +7770,7 @@
         <v>103</v>
       </c>
       <c r="C219" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D219" s="20">
         <v>2021</v>
@@ -7805,7 +7802,7 @@
         <v>151</v>
       </c>
       <c r="C220" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D220" s="20">
         <v>2021</v>
@@ -7837,7 +7834,7 @@
         <v>153</v>
       </c>
       <c r="C221" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D221" s="20">
         <v>2021</v>
@@ -7869,7 +7866,7 @@
         <v>154</v>
       </c>
       <c r="C222" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D222" s="20">
         <v>2021</v>
@@ -7901,7 +7898,7 @@
         <v>155</v>
       </c>
       <c r="C223" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D223" s="20">
         <v>2021</v>
@@ -7933,7 +7930,7 @@
         <v>157</v>
       </c>
       <c r="C224" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D224" s="20">
         <v>2021</v>
@@ -7965,7 +7962,7 @@
         <v>158</v>
       </c>
       <c r="C225" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D225" s="20">
         <v>2021</v>
@@ -7997,7 +7994,7 @@
         <v>159</v>
       </c>
       <c r="C226" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D226" s="20">
         <v>2021</v>
@@ -8029,7 +8026,7 @@
         <v>1</v>
       </c>
       <c r="C227" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D227" s="20">
         <v>2021</v>
@@ -8061,7 +8058,7 @@
         <v>241</v>
       </c>
       <c r="C228" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D228" s="16">
         <v>2021</v>
@@ -8093,7 +8090,7 @@
         <v>241001</v>
       </c>
       <c r="C229" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D229" s="20">
         <v>2021</v>
@@ -8125,7 +8122,7 @@
         <v>241999</v>
       </c>
       <c r="C230" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D230" s="20">
         <v>2021</v>
@@ -8157,7 +8154,7 @@
         <v>251</v>
       </c>
       <c r="C231" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D231" s="20">
         <v>2021</v>
@@ -8189,7 +8186,7 @@
         <v>252</v>
       </c>
       <c r="C232" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D232" s="20">
         <v>2021</v>
@@ -8221,7 +8218,7 @@
         <v>254</v>
       </c>
       <c r="C233" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D233" s="20">
         <v>2021</v>
@@ -8253,7 +8250,7 @@
         <v>255</v>
       </c>
       <c r="C234" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D234" s="20">
         <v>2021</v>
@@ -8285,7 +8282,7 @@
         <v>256</v>
       </c>
       <c r="C235" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D235" s="20">
         <v>2021</v>
@@ -8317,7 +8314,7 @@
         <v>257</v>
       </c>
       <c r="C236" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D236" s="20">
         <v>2021</v>
@@ -8349,7 +8346,7 @@
         <v>2</v>
       </c>
       <c r="C237" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D237" s="20">
         <v>2021</v>
@@ -8381,7 +8378,7 @@
         <v>351</v>
       </c>
       <c r="C238" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D238" s="16">
         <v>2021</v>
@@ -8413,7 +8410,7 @@
         <v>352</v>
       </c>
       <c r="C239" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D239" s="20">
         <v>2021</v>
@@ -8445,7 +8442,7 @@
         <v>353</v>
       </c>
       <c r="C240" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D240" s="20">
         <v>2021</v>
@@ -8477,7 +8474,7 @@
         <v>12</v>
       </c>
       <c r="C241" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D241" s="20">
         <v>2021</v>
@@ -8509,7 +8506,7 @@
         <v>355</v>
       </c>
       <c r="C242" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D242" s="20">
         <v>2021</v>
@@ -8541,7 +8538,7 @@
         <v>356</v>
       </c>
       <c r="C243" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D243" s="20">
         <v>2021</v>
@@ -8573,7 +8570,7 @@
         <v>357</v>
       </c>
       <c r="C244" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D244" s="20">
         <v>2021</v>
@@ -8605,7 +8602,7 @@
         <v>358</v>
       </c>
       <c r="C245" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D245" s="20">
         <v>2021</v>
@@ -8637,7 +8634,7 @@
         <v>359</v>
       </c>
       <c r="C246" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D246" s="20">
         <v>2021</v>
@@ -8669,7 +8666,7 @@
         <v>12</v>
       </c>
       <c r="C247" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D247" s="20">
         <v>2021</v>
@@ -8701,7 +8698,7 @@
         <v>361</v>
       </c>
       <c r="C248" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D248" s="20">
         <v>2021</v>
@@ -8733,7 +8730,7 @@
         <v>3</v>
       </c>
       <c r="C249" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D249" s="20">
         <v>2021</v>
@@ -8765,7 +8762,7 @@
         <v>401</v>
       </c>
       <c r="C250" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D250" s="16">
         <v>2021</v>
@@ -8797,7 +8794,7 @@
         <v>13</v>
       </c>
       <c r="C251" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D251" s="20">
         <v>2021</v>
@@ -8829,7 +8826,7 @@
         <v>403</v>
       </c>
       <c r="C252" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D252" s="20">
         <v>2021</v>
@@ -8861,7 +8858,7 @@
         <v>404</v>
       </c>
       <c r="C253" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D253" s="20">
         <v>2021</v>
@@ -8893,7 +8890,7 @@
         <v>405</v>
       </c>
       <c r="C254" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D254" s="20">
         <v>2021</v>
@@ -8925,7 +8922,7 @@
         <v>451</v>
       </c>
       <c r="C255" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D255" s="20">
         <v>2021</v>
@@ -8957,7 +8954,7 @@
         <v>452</v>
       </c>
       <c r="C256" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D256" s="20">
         <v>2021</v>
@@ -8989,7 +8986,7 @@
         <v>453</v>
       </c>
       <c r="C257" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D257" s="20">
         <v>2021</v>
@@ -9021,7 +9018,7 @@
         <v>454</v>
       </c>
       <c r="C258" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D258" s="20">
         <v>2021</v>
@@ -9053,7 +9050,7 @@
         <v>14</v>
       </c>
       <c r="C259" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D259" s="20">
         <v>2021</v>
@@ -9085,7 +9082,7 @@
         <v>456</v>
       </c>
       <c r="C260" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D260" s="20">
         <v>2021</v>
@@ -9117,7 +9114,7 @@
         <v>13</v>
       </c>
       <c r="C261" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D261" s="20">
         <v>2021</v>
@@ -9149,7 +9146,7 @@
         <v>458</v>
       </c>
       <c r="C262" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D262" s="20">
         <v>2021</v>
@@ -9181,7 +9178,7 @@
         <v>459</v>
       </c>
       <c r="C263" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D263" s="20">
         <v>2021</v>
@@ -9213,7 +9210,7 @@
         <v>460</v>
       </c>
       <c r="C264" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D264" s="20">
         <v>2021</v>
@@ -9245,7 +9242,7 @@
         <v>461</v>
       </c>
       <c r="C265" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D265" s="20">
         <v>2021</v>
@@ -9277,7 +9274,7 @@
         <v>14</v>
       </c>
       <c r="C266" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D266" s="20">
         <v>2021</v>
@@ -9309,7 +9306,7 @@
         <v>4</v>
       </c>
       <c r="C267" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D267" s="20">
         <v>2021</v>
@@ -9341,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="C268" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D268" s="16">
         <v>2021</v>
@@ -9373,7 +9370,7 @@
         <v>0</v>
       </c>
       <c r="C269" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D269" s="16">
         <v>2020</v>
@@ -9405,7 +9402,7 @@
         <v>101</v>
       </c>
       <c r="C270" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D270" s="20">
         <v>2019</v>
@@ -9437,7 +9434,7 @@
         <v>102</v>
       </c>
       <c r="C271" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D271" s="20">
         <v>2019</v>
@@ -9469,7 +9466,7 @@
         <v>103</v>
       </c>
       <c r="C272" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D272" s="20">
         <v>2019</v>
@@ -9501,7 +9498,7 @@
         <v>151</v>
       </c>
       <c r="C273" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D273" s="20">
         <v>2019</v>
@@ -9533,7 +9530,7 @@
         <v>153</v>
       </c>
       <c r="C274" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D274" s="20">
         <v>2019</v>
@@ -9565,7 +9562,7 @@
         <v>154</v>
       </c>
       <c r="C275" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D275" s="20">
         <v>2019</v>
@@ -9597,7 +9594,7 @@
         <v>155</v>
       </c>
       <c r="C276" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D276" s="20">
         <v>2019</v>
@@ -9629,7 +9626,7 @@
         <v>157</v>
       </c>
       <c r="C277" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D277" s="20">
         <v>2019</v>
@@ -9661,7 +9658,7 @@
         <v>158</v>
       </c>
       <c r="C278" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D278" s="20">
         <v>2019</v>
@@ -9693,7 +9690,7 @@
         <v>159</v>
       </c>
       <c r="C279" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D279" s="20">
         <v>2019</v>
@@ -9725,7 +9722,7 @@
         <v>1</v>
       </c>
       <c r="C280" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D280" s="16">
         <v>2019</v>
@@ -9757,7 +9754,7 @@
         <v>241</v>
       </c>
       <c r="C281" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D281" s="20">
         <v>2019</v>
@@ -9789,7 +9786,7 @@
         <v>241001</v>
       </c>
       <c r="C282" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D282" s="20">
         <v>2019</v>
@@ -9821,7 +9818,7 @@
         <v>241999</v>
       </c>
       <c r="C283" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D283" s="20">
         <v>2019</v>
@@ -9853,7 +9850,7 @@
         <v>251</v>
       </c>
       <c r="C284" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D284" s="20">
         <v>2019</v>
@@ -9885,7 +9882,7 @@
         <v>252</v>
       </c>
       <c r="C285" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D285" s="20">
         <v>2019</v>
@@ -9917,7 +9914,7 @@
         <v>254</v>
       </c>
       <c r="C286" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D286" s="20">
         <v>2019</v>
@@ -9949,7 +9946,7 @@
         <v>255</v>
       </c>
       <c r="C287" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D287" s="20">
         <v>2019</v>
@@ -9981,7 +9978,7 @@
         <v>256</v>
       </c>
       <c r="C288" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D288" s="20">
         <v>2019</v>
@@ -10013,7 +10010,7 @@
         <v>257</v>
       </c>
       <c r="C289" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D289" s="20">
         <v>2019</v>
@@ -10045,7 +10042,7 @@
         <v>2</v>
       </c>
       <c r="C290" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D290" s="16">
         <v>2019</v>
@@ -10077,7 +10074,7 @@
         <v>351</v>
       </c>
       <c r="C291" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D291" s="20">
         <v>2019</v>
@@ -10109,7 +10106,7 @@
         <v>352</v>
       </c>
       <c r="C292" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D292" s="20">
         <v>2019</v>
@@ -10141,7 +10138,7 @@
         <v>353</v>
       </c>
       <c r="C293" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D293" s="20">
         <v>2019</v>
@@ -10173,7 +10170,7 @@
         <v>12</v>
       </c>
       <c r="C294" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D294" s="20">
         <v>2019</v>
@@ -10205,7 +10202,7 @@
         <v>355</v>
       </c>
       <c r="C295" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D295" s="20">
         <v>2019</v>
@@ -10237,7 +10234,7 @@
         <v>356</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D296" s="20">
         <v>2019</v>
@@ -10269,7 +10266,7 @@
         <v>357</v>
       </c>
       <c r="C297" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D297" s="20">
         <v>2019</v>
@@ -10301,7 +10298,7 @@
         <v>358</v>
       </c>
       <c r="C298" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D298" s="20">
         <v>2019</v>
@@ -10333,7 +10330,7 @@
         <v>359</v>
       </c>
       <c r="C299" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D299" s="20">
         <v>2019</v>
@@ -10365,7 +10362,7 @@
         <v>12</v>
       </c>
       <c r="C300" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D300" s="20">
         <v>2019</v>
@@ -10397,7 +10394,7 @@
         <v>361</v>
       </c>
       <c r="C301" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D301" s="20">
         <v>2019</v>
@@ -10429,7 +10426,7 @@
         <v>3</v>
       </c>
       <c r="C302" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D302" s="16">
         <v>2019</v>
@@ -10461,7 +10458,7 @@
         <v>401</v>
       </c>
       <c r="C303" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D303" s="20">
         <v>2019</v>
@@ -10493,7 +10490,7 @@
         <v>13</v>
       </c>
       <c r="C304" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D304" s="20">
         <v>2019</v>
@@ -10525,7 +10522,7 @@
         <v>403</v>
       </c>
       <c r="C305" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D305" s="20">
         <v>2019</v>
@@ -10557,7 +10554,7 @@
         <v>404</v>
       </c>
       <c r="C306" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D306" s="20">
         <v>2019</v>
@@ -10589,7 +10586,7 @@
         <v>405</v>
       </c>
       <c r="C307" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D307" s="20">
         <v>2019</v>
@@ -10621,7 +10618,7 @@
         <v>451</v>
       </c>
       <c r="C308" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D308" s="20">
         <v>2019</v>
@@ -10653,7 +10650,7 @@
         <v>452</v>
       </c>
       <c r="C309" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D309" s="20">
         <v>2019</v>
@@ -10685,7 +10682,7 @@
         <v>453</v>
       </c>
       <c r="C310" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D310" s="20">
         <v>2019</v>
@@ -10717,7 +10714,7 @@
         <v>454</v>
       </c>
       <c r="C311" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D311" s="20">
         <v>2019</v>
@@ -10749,7 +10746,7 @@
         <v>14</v>
       </c>
       <c r="C312" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D312" s="20">
         <v>2019</v>
@@ -10781,7 +10778,7 @@
         <v>456</v>
       </c>
       <c r="C313" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D313" s="20">
         <v>2019</v>
@@ -10813,7 +10810,7 @@
         <v>13</v>
       </c>
       <c r="C314" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D314" s="20">
         <v>2019</v>
@@ -10845,7 +10842,7 @@
         <v>458</v>
       </c>
       <c r="C315" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D315" s="20">
         <v>2019</v>
@@ -10877,7 +10874,7 @@
         <v>459</v>
       </c>
       <c r="C316" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D316" s="20">
         <v>2019</v>
@@ -10909,7 +10906,7 @@
         <v>460</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D317" s="20">
         <v>2019</v>
@@ -10941,7 +10938,7 @@
         <v>461</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D318" s="20">
         <v>2019</v>
@@ -10973,7 +10970,7 @@
         <v>14</v>
       </c>
       <c r="C319" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D319" s="20">
         <v>2019</v>
@@ -11005,7 +11002,7 @@
         <v>4</v>
       </c>
       <c r="C320" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D320" s="16">
         <v>2019</v>
@@ -11037,7 +11034,7 @@
         <v>0</v>
       </c>
       <c r="C321" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D321" s="16">
         <v>2019</v>
@@ -11069,7 +11066,7 @@
         <v>101</v>
       </c>
       <c r="C322" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D322" s="20">
         <v>2018</v>
@@ -11101,7 +11098,7 @@
         <v>102</v>
       </c>
       <c r="C323" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D323" s="20">
         <v>2018</v>
@@ -11133,7 +11130,7 @@
         <v>103</v>
       </c>
       <c r="C324" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D324" s="20">
         <v>2018</v>
@@ -11165,7 +11162,7 @@
         <v>151</v>
       </c>
       <c r="C325" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D325" s="20">
         <v>2018</v>
@@ -11197,7 +11194,7 @@
         <v>153</v>
       </c>
       <c r="C326" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D326" s="20">
         <v>2018</v>
@@ -11229,7 +11226,7 @@
         <v>154</v>
       </c>
       <c r="C327" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D327" s="20">
         <v>2018</v>
@@ -11261,7 +11258,7 @@
         <v>155</v>
       </c>
       <c r="C328" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D328" s="20">
         <v>2018</v>
@@ -11293,7 +11290,7 @@
         <v>157</v>
       </c>
       <c r="C329" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D329" s="20">
         <v>2018</v>
@@ -11325,7 +11322,7 @@
         <v>158</v>
       </c>
       <c r="C330" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D330" s="20">
         <v>2018</v>
@@ -11357,7 +11354,7 @@
         <v>159</v>
       </c>
       <c r="C331" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D331" s="20">
         <v>2018</v>
@@ -11389,7 +11386,7 @@
         <v>1</v>
       </c>
       <c r="C332" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D332" s="16">
         <v>2018</v>
@@ -11421,7 +11418,7 @@
         <v>241</v>
       </c>
       <c r="C333" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D333" s="20">
         <v>2018</v>
@@ -11453,7 +11450,7 @@
         <v>241001</v>
       </c>
       <c r="C334" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D334" s="20">
         <v>2018</v>
@@ -11485,7 +11482,7 @@
         <v>241999</v>
       </c>
       <c r="C335" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D335" s="20">
         <v>2018</v>
@@ -11517,7 +11514,7 @@
         <v>251</v>
       </c>
       <c r="C336" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D336" s="20">
         <v>2018</v>
@@ -11549,7 +11546,7 @@
         <v>252</v>
       </c>
       <c r="C337" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D337" s="20">
         <v>2018</v>
@@ -11581,7 +11578,7 @@
         <v>254</v>
       </c>
       <c r="C338" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D338" s="20">
         <v>2018</v>
@@ -11613,7 +11610,7 @@
         <v>255</v>
       </c>
       <c r="C339" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D339" s="20">
         <v>2018</v>
@@ -11645,7 +11642,7 @@
         <v>256</v>
       </c>
       <c r="C340" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D340" s="20">
         <v>2018</v>
@@ -11677,7 +11674,7 @@
         <v>257</v>
       </c>
       <c r="C341" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D341" s="20">
         <v>2018</v>
@@ -11709,7 +11706,7 @@
         <v>2</v>
       </c>
       <c r="C342" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D342" s="16">
         <v>2018</v>
@@ -11741,7 +11738,7 @@
         <v>351</v>
       </c>
       <c r="C343" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D343" s="20">
         <v>2018</v>
@@ -11773,7 +11770,7 @@
         <v>352</v>
       </c>
       <c r="C344" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D344" s="20">
         <v>2018</v>
@@ -11805,7 +11802,7 @@
         <v>353</v>
       </c>
       <c r="C345" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D345" s="20">
         <v>2018</v>
@@ -11837,7 +11834,7 @@
         <v>12</v>
       </c>
       <c r="C346" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D346" s="20">
         <v>2018</v>
@@ -11869,7 +11866,7 @@
         <v>355</v>
       </c>
       <c r="C347" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D347" s="20">
         <v>2018</v>
@@ -11901,7 +11898,7 @@
         <v>356</v>
       </c>
       <c r="C348" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D348" s="20">
         <v>2018</v>
@@ -11933,7 +11930,7 @@
         <v>357</v>
       </c>
       <c r="C349" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D349" s="20">
         <v>2018</v>
@@ -11965,7 +11962,7 @@
         <v>358</v>
       </c>
       <c r="C350" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D350" s="20">
         <v>2018</v>
@@ -11997,7 +11994,7 @@
         <v>359</v>
       </c>
       <c r="C351" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D351" s="20">
         <v>2018</v>
@@ -12029,7 +12026,7 @@
         <v>12</v>
       </c>
       <c r="C352" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D352" s="20">
         <v>2018</v>
@@ -12061,7 +12058,7 @@
         <v>361</v>
       </c>
       <c r="C353" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D353" s="20">
         <v>2018</v>
@@ -12093,7 +12090,7 @@
         <v>3</v>
       </c>
       <c r="C354" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D354" s="16">
         <v>2018</v>
@@ -12125,7 +12122,7 @@
         <v>401</v>
       </c>
       <c r="C355" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D355" s="20">
         <v>2018</v>
@@ -12157,7 +12154,7 @@
         <v>13</v>
       </c>
       <c r="C356" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D356" s="20">
         <v>2018</v>
@@ -12189,7 +12186,7 @@
         <v>403</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D357" s="20">
         <v>2018</v>
@@ -12221,7 +12218,7 @@
         <v>404</v>
       </c>
       <c r="C358" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D358" s="20">
         <v>2018</v>
@@ -12253,7 +12250,7 @@
         <v>405</v>
       </c>
       <c r="C359" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D359" s="20">
         <v>2018</v>
@@ -12285,7 +12282,7 @@
         <v>451</v>
       </c>
       <c r="C360" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D360" s="20">
         <v>2018</v>
@@ -12317,7 +12314,7 @@
         <v>452</v>
       </c>
       <c r="C361" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D361" s="20">
         <v>2018</v>
@@ -12349,7 +12346,7 @@
         <v>453</v>
       </c>
       <c r="C362" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D362" s="20">
         <v>2018</v>
@@ -12381,7 +12378,7 @@
         <v>454</v>
       </c>
       <c r="C363" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D363" s="20">
         <v>2018</v>
@@ -12413,7 +12410,7 @@
         <v>14</v>
       </c>
       <c r="C364" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D364" s="20">
         <v>2018</v>
@@ -12445,7 +12442,7 @@
         <v>456</v>
       </c>
       <c r="C365" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D365" s="20">
         <v>2018</v>
@@ -12477,7 +12474,7 @@
         <v>13</v>
       </c>
       <c r="C366" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D366" s="20">
         <v>2018</v>
@@ -12509,7 +12506,7 @@
         <v>458</v>
       </c>
       <c r="C367" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D367" s="20">
         <v>2018</v>
@@ -12541,7 +12538,7 @@
         <v>459</v>
       </c>
       <c r="C368" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D368" s="20">
         <v>2018</v>
@@ -12573,7 +12570,7 @@
         <v>460</v>
       </c>
       <c r="C369" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D369" s="20">
         <v>2018</v>
@@ -12605,7 +12602,7 @@
         <v>461</v>
       </c>
       <c r="C370" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D370" s="20">
         <v>2018</v>
@@ -12637,7 +12634,7 @@
         <v>14</v>
       </c>
       <c r="C371" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D371" s="20">
         <v>2018</v>
@@ -12669,7 +12666,7 @@
         <v>4</v>
       </c>
       <c r="C372" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D372" s="16">
         <v>2018</v>
@@ -12701,7 +12698,7 @@
         <v>0</v>
       </c>
       <c r="C373" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D373" s="16">
         <v>2018</v>
@@ -12733,7 +12730,7 @@
         <v>101</v>
       </c>
       <c r="C374" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D374" s="20">
         <v>2017</v>
@@ -12765,7 +12762,7 @@
         <v>102</v>
       </c>
       <c r="C375" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D375" s="20">
         <v>2017</v>
@@ -12797,7 +12794,7 @@
         <v>103</v>
       </c>
       <c r="C376" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D376" s="20">
         <v>2017</v>
@@ -12829,7 +12826,7 @@
         <v>151</v>
       </c>
       <c r="C377" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D377" s="20">
         <v>2017</v>
@@ -12861,7 +12858,7 @@
         <v>153</v>
       </c>
       <c r="C378" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D378" s="20">
         <v>2017</v>
@@ -12893,7 +12890,7 @@
         <v>154</v>
       </c>
       <c r="C379" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D379" s="20">
         <v>2017</v>
@@ -12925,7 +12922,7 @@
         <v>155</v>
       </c>
       <c r="C380" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D380" s="20">
         <v>2017</v>
@@ -12957,7 +12954,7 @@
         <v>157</v>
       </c>
       <c r="C381" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D381" s="20">
         <v>2017</v>
@@ -12989,7 +12986,7 @@
         <v>158</v>
       </c>
       <c r="C382" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D382" s="20">
         <v>2017</v>
@@ -13021,7 +13018,7 @@
         <v>159</v>
       </c>
       <c r="C383" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D383" s="20">
         <v>2017</v>
@@ -13053,7 +13050,7 @@
         <v>1</v>
       </c>
       <c r="C384" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D384" s="16">
         <v>2017</v>
@@ -13085,7 +13082,7 @@
         <v>241</v>
       </c>
       <c r="C385" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D385" s="20">
         <v>2017</v>
@@ -13117,7 +13114,7 @@
         <v>241001</v>
       </c>
       <c r="C386" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D386" s="20">
         <v>2017</v>
@@ -13149,7 +13146,7 @@
         <v>241999</v>
       </c>
       <c r="C387" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D387" s="20">
         <v>2017</v>
@@ -13181,7 +13178,7 @@
         <v>251</v>
       </c>
       <c r="C388" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D388" s="20">
         <v>2017</v>
@@ -13213,7 +13210,7 @@
         <v>252</v>
       </c>
       <c r="C389" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D389" s="20">
         <v>2017</v>
@@ -13245,7 +13242,7 @@
         <v>254</v>
       </c>
       <c r="C390" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D390" s="20">
         <v>2017</v>
@@ -13277,7 +13274,7 @@
         <v>255</v>
       </c>
       <c r="C391" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D391" s="20">
         <v>2017</v>
@@ -13309,7 +13306,7 @@
         <v>256</v>
       </c>
       <c r="C392" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D392" s="20">
         <v>2017</v>
@@ -13341,7 +13338,7 @@
         <v>257</v>
       </c>
       <c r="C393" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D393" s="20">
         <v>2017</v>
@@ -13373,7 +13370,7 @@
         <v>2</v>
       </c>
       <c r="C394" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D394" s="16">
         <v>2017</v>
@@ -13405,7 +13402,7 @@
         <v>351</v>
       </c>
       <c r="C395" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D395" s="20">
         <v>2017</v>
@@ -13437,7 +13434,7 @@
         <v>352</v>
       </c>
       <c r="C396" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D396" s="20">
         <v>2017</v>
@@ -13469,7 +13466,7 @@
         <v>353</v>
       </c>
       <c r="C397" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D397" s="20">
         <v>2017</v>
@@ -13501,7 +13498,7 @@
         <v>12</v>
       </c>
       <c r="C398" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D398" s="20">
         <v>2017</v>
@@ -13533,7 +13530,7 @@
         <v>355</v>
       </c>
       <c r="C399" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D399" s="20">
         <v>2017</v>
@@ -13565,7 +13562,7 @@
         <v>356</v>
       </c>
       <c r="C400" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D400" s="20">
         <v>2017</v>
@@ -13597,7 +13594,7 @@
         <v>357</v>
       </c>
       <c r="C401" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D401" s="20">
         <v>2017</v>
@@ -13629,7 +13626,7 @@
         <v>358</v>
       </c>
       <c r="C402" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D402" s="20">
         <v>2017</v>
@@ -13661,7 +13658,7 @@
         <v>359</v>
       </c>
       <c r="C403" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D403" s="20">
         <v>2017</v>
@@ -13693,7 +13690,7 @@
         <v>12</v>
       </c>
       <c r="C404" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D404" s="20">
         <v>2017</v>
@@ -13725,7 +13722,7 @@
         <v>361</v>
       </c>
       <c r="C405" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D405" s="20">
         <v>2017</v>
@@ -13757,7 +13754,7 @@
         <v>3</v>
       </c>
       <c r="C406" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D406" s="16">
         <v>2017</v>
@@ -13789,7 +13786,7 @@
         <v>401</v>
       </c>
       <c r="C407" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D407" s="20">
         <v>2017</v>
@@ -13821,7 +13818,7 @@
         <v>13</v>
       </c>
       <c r="C408" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D408" s="20">
         <v>2017</v>
@@ -13853,7 +13850,7 @@
         <v>403</v>
       </c>
       <c r="C409" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D409" s="20">
         <v>2017</v>
@@ -13885,7 +13882,7 @@
         <v>404</v>
       </c>
       <c r="C410" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D410" s="20">
         <v>2017</v>
@@ -13917,7 +13914,7 @@
         <v>405</v>
       </c>
       <c r="C411" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D411" s="20">
         <v>2017</v>
@@ -13949,7 +13946,7 @@
         <v>451</v>
       </c>
       <c r="C412" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D412" s="20">
         <v>2017</v>
@@ -13981,7 +13978,7 @@
         <v>452</v>
       </c>
       <c r="C413" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D413" s="20">
         <v>2017</v>
@@ -14013,7 +14010,7 @@
         <v>453</v>
       </c>
       <c r="C414" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D414" s="20">
         <v>2017</v>
@@ -14045,7 +14042,7 @@
         <v>454</v>
       </c>
       <c r="C415" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D415" s="20">
         <v>2017</v>
@@ -14077,7 +14074,7 @@
         <v>14</v>
       </c>
       <c r="C416" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D416" s="20">
         <v>2017</v>
@@ -14109,7 +14106,7 @@
         <v>456</v>
       </c>
       <c r="C417" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D417" s="20">
         <v>2017</v>
@@ -14141,7 +14138,7 @@
         <v>13</v>
       </c>
       <c r="C418" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D418" s="20">
         <v>2017</v>
@@ -14173,7 +14170,7 @@
         <v>458</v>
       </c>
       <c r="C419" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D419" s="20">
         <v>2017</v>
@@ -14205,7 +14202,7 @@
         <v>459</v>
       </c>
       <c r="C420" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D420" s="20">
         <v>2017</v>
@@ -14237,7 +14234,7 @@
         <v>460</v>
       </c>
       <c r="C421" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D421" s="20">
         <v>2017</v>
@@ -14269,7 +14266,7 @@
         <v>461</v>
       </c>
       <c r="C422" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D422" s="20">
         <v>2017</v>
@@ -14301,7 +14298,7 @@
         <v>14</v>
       </c>
       <c r="C423" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D423" s="20">
         <v>2017</v>
@@ -14333,7 +14330,7 @@
         <v>4</v>
       </c>
       <c r="C424" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D424" s="16">
         <v>2017</v>
@@ -14365,7 +14362,7 @@
         <v>0</v>
       </c>
       <c r="C425" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D425" s="16">
         <v>2017</v>
@@ -14397,7 +14394,7 @@
         <v>101</v>
       </c>
       <c r="C426" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D426" s="20">
         <v>2016</v>
@@ -14429,7 +14426,7 @@
         <v>102</v>
       </c>
       <c r="C427" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D427" s="20">
         <v>2016</v>
@@ -14461,7 +14458,7 @@
         <v>103</v>
       </c>
       <c r="C428" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D428" s="20">
         <v>2016</v>
@@ -14493,7 +14490,7 @@
         <v>151</v>
       </c>
       <c r="C429" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D429" s="20">
         <v>2016</v>
@@ -14525,7 +14522,7 @@
         <v>153</v>
       </c>
       <c r="C430" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D430" s="20">
         <v>2016</v>
@@ -14557,7 +14554,7 @@
         <v>154</v>
       </c>
       <c r="C431" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D431" s="20">
         <v>2016</v>
@@ -14589,7 +14586,7 @@
         <v>155</v>
       </c>
       <c r="C432" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D432" s="20">
         <v>2016</v>
@@ -14621,7 +14618,7 @@
         <v>157</v>
       </c>
       <c r="C433" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D433" s="20">
         <v>2016</v>
@@ -14653,7 +14650,7 @@
         <v>158</v>
       </c>
       <c r="C434" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D434" s="20">
         <v>2016</v>
@@ -14685,7 +14682,7 @@
         <v>159</v>
       </c>
       <c r="C435" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D435" s="20">
         <v>2016</v>
@@ -14717,7 +14714,7 @@
         <v>1</v>
       </c>
       <c r="C436" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D436" s="16">
         <v>2016</v>
@@ -14749,7 +14746,7 @@
         <v>241</v>
       </c>
       <c r="C437" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D437" s="20">
         <v>2016</v>
@@ -14781,7 +14778,7 @@
         <v>241001</v>
       </c>
       <c r="C438" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D438" s="20">
         <v>2016</v>
@@ -14813,7 +14810,7 @@
         <v>241999</v>
       </c>
       <c r="C439" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D439" s="20">
         <v>2016</v>
@@ -14845,7 +14842,7 @@
         <v>251</v>
       </c>
       <c r="C440" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D440" s="20">
         <v>2016</v>
@@ -14877,7 +14874,7 @@
         <v>252</v>
       </c>
       <c r="C441" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D441" s="20">
         <v>2016</v>
@@ -14909,7 +14906,7 @@
         <v>254</v>
       </c>
       <c r="C442" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D442" s="20">
         <v>2016</v>
@@ -14941,7 +14938,7 @@
         <v>255</v>
       </c>
       <c r="C443" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D443" s="20">
         <v>2016</v>
@@ -14973,7 +14970,7 @@
         <v>256</v>
       </c>
       <c r="C444" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D444" s="20">
         <v>2016</v>
@@ -15005,7 +15002,7 @@
         <v>257</v>
       </c>
       <c r="C445" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D445" s="20">
         <v>2016</v>
@@ -15037,7 +15034,7 @@
         <v>2</v>
       </c>
       <c r="C446" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D446" s="16">
         <v>2016</v>
@@ -15069,7 +15066,7 @@
         <v>351</v>
       </c>
       <c r="C447" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D447" s="20">
         <v>2016</v>
@@ -15101,7 +15098,7 @@
         <v>352</v>
       </c>
       <c r="C448" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D448" s="20">
         <v>2016</v>
@@ -15133,7 +15130,7 @@
         <v>353</v>
       </c>
       <c r="C449" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D449" s="20">
         <v>2016</v>
@@ -15165,7 +15162,7 @@
         <v>12</v>
       </c>
       <c r="C450" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D450" s="20">
         <v>2016</v>
@@ -15197,7 +15194,7 @@
         <v>355</v>
       </c>
       <c r="C451" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D451" s="20">
         <v>2016</v>
@@ -15229,7 +15226,7 @@
         <v>356</v>
       </c>
       <c r="C452" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D452" s="20">
         <v>2016</v>
@@ -15261,7 +15258,7 @@
         <v>357</v>
       </c>
       <c r="C453" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D453" s="20">
         <v>2016</v>
@@ -15293,7 +15290,7 @@
         <v>358</v>
       </c>
       <c r="C454" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D454" s="20">
         <v>2016</v>
@@ -15325,7 +15322,7 @@
         <v>359</v>
       </c>
       <c r="C455" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D455" s="20">
         <v>2016</v>
@@ -15357,7 +15354,7 @@
         <v>12</v>
       </c>
       <c r="C456" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D456" s="20">
         <v>2016</v>
@@ -15389,7 +15386,7 @@
         <v>361</v>
       </c>
       <c r="C457" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D457" s="20">
         <v>2016</v>
@@ -15421,7 +15418,7 @@
         <v>3</v>
       </c>
       <c r="C458" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D458" s="16">
         <v>2016</v>
@@ -15453,7 +15450,7 @@
         <v>401</v>
       </c>
       <c r="C459" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D459" s="20">
         <v>2016</v>
@@ -15485,7 +15482,7 @@
         <v>13</v>
       </c>
       <c r="C460" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D460" s="20">
         <v>2016</v>
@@ -15517,7 +15514,7 @@
         <v>403</v>
       </c>
       <c r="C461" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D461" s="20">
         <v>2016</v>
@@ -15549,7 +15546,7 @@
         <v>404</v>
       </c>
       <c r="C462" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D462" s="20">
         <v>2016</v>
@@ -15581,7 +15578,7 @@
         <v>405</v>
       </c>
       <c r="C463" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D463" s="20">
         <v>2016</v>
@@ -15613,7 +15610,7 @@
         <v>451</v>
       </c>
       <c r="C464" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D464" s="20">
         <v>2016</v>
@@ -15645,7 +15642,7 @@
         <v>452</v>
       </c>
       <c r="C465" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D465" s="20">
         <v>2016</v>
@@ -15677,7 +15674,7 @@
         <v>453</v>
       </c>
       <c r="C466" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D466" s="20">
         <v>2016</v>
@@ -15709,7 +15706,7 @@
         <v>454</v>
       </c>
       <c r="C467" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D467" s="20">
         <v>2016</v>
@@ -15741,7 +15738,7 @@
         <v>14</v>
       </c>
       <c r="C468" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D468" s="20">
         <v>2016</v>
@@ -15773,7 +15770,7 @@
         <v>456</v>
       </c>
       <c r="C469" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D469" s="20">
         <v>2016</v>
@@ -15805,7 +15802,7 @@
         <v>13</v>
       </c>
       <c r="C470" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D470" s="20">
         <v>2016</v>
@@ -15837,7 +15834,7 @@
         <v>458</v>
       </c>
       <c r="C471" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D471" s="20">
         <v>2016</v>
@@ -15869,7 +15866,7 @@
         <v>459</v>
       </c>
       <c r="C472" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D472" s="20">
         <v>2016</v>
@@ -15901,7 +15898,7 @@
         <v>460</v>
       </c>
       <c r="C473" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D473" s="20">
         <v>2016</v>
@@ -15933,7 +15930,7 @@
         <v>461</v>
       </c>
       <c r="C474" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D474" s="20">
         <v>2016</v>
@@ -15965,7 +15962,7 @@
         <v>14</v>
       </c>
       <c r="C475" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D475" s="20">
         <v>2016</v>
@@ -15997,7 +15994,7 @@
         <v>4</v>
       </c>
       <c r="C476" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D476" s="16">
         <v>2016</v>
@@ -16029,7 +16026,7 @@
         <v>0</v>
       </c>
       <c r="C477" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D477" s="16">
         <v>2016</v>
@@ -16061,7 +16058,7 @@
         <v>101</v>
       </c>
       <c r="C478" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D478" s="20">
         <v>2015</v>
@@ -16093,7 +16090,7 @@
         <v>102</v>
       </c>
       <c r="C479" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D479" s="20">
         <v>2015</v>
@@ -16125,7 +16122,7 @@
         <v>103</v>
       </c>
       <c r="C480" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D480" s="20">
         <v>2015</v>
@@ -16157,7 +16154,7 @@
         <v>151</v>
       </c>
       <c r="C481" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D481" s="20">
         <v>2015</v>
@@ -16189,7 +16186,7 @@
         <v>153</v>
       </c>
       <c r="C482" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D482" s="20">
         <v>2015</v>
@@ -16221,7 +16218,7 @@
         <v>154</v>
       </c>
       <c r="C483" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D483" s="20">
         <v>2015</v>
@@ -16253,7 +16250,7 @@
         <v>155</v>
       </c>
       <c r="C484" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D484" s="20">
         <v>2015</v>
@@ -16285,7 +16282,7 @@
         <v>157</v>
       </c>
       <c r="C485" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D485" s="20">
         <v>2015</v>
@@ -16317,7 +16314,7 @@
         <v>158</v>
       </c>
       <c r="C486" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D486" s="20">
         <v>2015</v>
@@ -16349,7 +16346,7 @@
         <v>159</v>
       </c>
       <c r="C487" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D487" s="20">
         <v>2015</v>
@@ -16381,7 +16378,7 @@
         <v>1</v>
       </c>
       <c r="C488" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D488" s="16">
         <v>2015</v>
@@ -16413,7 +16410,7 @@
         <v>241</v>
       </c>
       <c r="C489" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D489" s="20">
         <v>2015</v>
@@ -16445,7 +16442,7 @@
         <v>241001</v>
       </c>
       <c r="C490" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D490" s="20">
         <v>2015</v>
@@ -16477,7 +16474,7 @@
         <v>241999</v>
       </c>
       <c r="C491" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D491" s="20">
         <v>2015</v>
@@ -16509,7 +16506,7 @@
         <v>251</v>
       </c>
       <c r="C492" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D492" s="20">
         <v>2015</v>
@@ -16541,7 +16538,7 @@
         <v>252</v>
       </c>
       <c r="C493" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D493" s="20">
         <v>2015</v>
@@ -16573,7 +16570,7 @@
         <v>254</v>
       </c>
       <c r="C494" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D494" s="20">
         <v>2015</v>
@@ -16605,7 +16602,7 @@
         <v>255</v>
       </c>
       <c r="C495" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D495" s="20">
         <v>2015</v>
@@ -16637,7 +16634,7 @@
         <v>256</v>
       </c>
       <c r="C496" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D496" s="20">
         <v>2015</v>
@@ -16669,7 +16666,7 @@
         <v>257</v>
       </c>
       <c r="C497" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D497" s="20">
         <v>2015</v>
@@ -16701,7 +16698,7 @@
         <v>2</v>
       </c>
       <c r="C498" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D498" s="16">
         <v>2015</v>
@@ -16733,7 +16730,7 @@
         <v>351</v>
       </c>
       <c r="C499" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D499" s="20">
         <v>2015</v>
@@ -16765,7 +16762,7 @@
         <v>352</v>
       </c>
       <c r="C500" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D500" s="20">
         <v>2015</v>
@@ -16797,7 +16794,7 @@
         <v>353</v>
       </c>
       <c r="C501" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D501" s="20">
         <v>2015</v>
@@ -16829,7 +16826,7 @@
         <v>12</v>
       </c>
       <c r="C502" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D502" s="20">
         <v>2015</v>
@@ -16861,7 +16858,7 @@
         <v>355</v>
       </c>
       <c r="C503" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D503" s="20">
         <v>2015</v>
@@ -16893,7 +16890,7 @@
         <v>356</v>
       </c>
       <c r="C504" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D504" s="20">
         <v>2015</v>
@@ -16925,7 +16922,7 @@
         <v>357</v>
       </c>
       <c r="C505" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D505" s="20">
         <v>2015</v>
@@ -16957,7 +16954,7 @@
         <v>358</v>
       </c>
       <c r="C506" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D506" s="20">
         <v>2015</v>
@@ -16989,7 +16986,7 @@
         <v>359</v>
       </c>
       <c r="C507" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D507" s="20">
         <v>2015</v>
@@ -17021,7 +17018,7 @@
         <v>12</v>
       </c>
       <c r="C508" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D508" s="20">
         <v>2015</v>
@@ -17053,7 +17050,7 @@
         <v>361</v>
       </c>
       <c r="C509" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D509" s="20">
         <v>2015</v>
@@ -17085,7 +17082,7 @@
         <v>3</v>
       </c>
       <c r="C510" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D510" s="16">
         <v>2015</v>
@@ -17117,7 +17114,7 @@
         <v>401</v>
       </c>
       <c r="C511" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D511" s="20">
         <v>2015</v>
@@ -17149,7 +17146,7 @@
         <v>13</v>
       </c>
       <c r="C512" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D512" s="20">
         <v>2015</v>
@@ -17181,7 +17178,7 @@
         <v>403</v>
       </c>
       <c r="C513" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D513" s="20">
         <v>2015</v>
@@ -17213,7 +17210,7 @@
         <v>404</v>
       </c>
       <c r="C514" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D514" s="20">
         <v>2015</v>
@@ -17245,7 +17242,7 @@
         <v>405</v>
       </c>
       <c r="C515" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D515" s="20">
         <v>2015</v>
@@ -17277,7 +17274,7 @@
         <v>451</v>
       </c>
       <c r="C516" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D516" s="20">
         <v>2015</v>
@@ -17309,7 +17306,7 @@
         <v>452</v>
       </c>
       <c r="C517" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D517" s="20">
         <v>2015</v>
@@ -17341,7 +17338,7 @@
         <v>453</v>
       </c>
       <c r="C518" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D518" s="20">
         <v>2015</v>
@@ -17373,7 +17370,7 @@
         <v>454</v>
       </c>
       <c r="C519" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D519" s="20">
         <v>2015</v>
@@ -17405,7 +17402,7 @@
         <v>14</v>
       </c>
       <c r="C520" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D520" s="20">
         <v>2015</v>
@@ -17437,7 +17434,7 @@
         <v>456</v>
       </c>
       <c r="C521" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D521" s="20">
         <v>2015</v>
@@ -17469,7 +17466,7 @@
         <v>13</v>
       </c>
       <c r="C522" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D522" s="20">
         <v>2015</v>
@@ -17501,7 +17498,7 @@
         <v>458</v>
       </c>
       <c r="C523" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D523" s="20">
         <v>2015</v>
@@ -17533,7 +17530,7 @@
         <v>459</v>
       </c>
       <c r="C524" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D524" s="20">
         <v>2015</v>
@@ -17565,7 +17562,7 @@
         <v>460</v>
       </c>
       <c r="C525" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D525" s="20">
         <v>2015</v>
@@ -17597,7 +17594,7 @@
         <v>461</v>
       </c>
       <c r="C526" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D526" s="20">
         <v>2015</v>
@@ -17629,7 +17626,7 @@
         <v>14</v>
       </c>
       <c r="C527" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D527" s="20">
         <v>2015</v>
@@ -17661,7 +17658,7 @@
         <v>4</v>
       </c>
       <c r="C528" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D528" s="16">
         <v>2015</v>
@@ -17693,7 +17690,7 @@
         <v>0</v>
       </c>
       <c r="C529" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D529" s="16">
         <v>2015</v>
@@ -17725,7 +17722,7 @@
         <v>101</v>
       </c>
       <c r="C530" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D530" s="20">
         <v>2014</v>
@@ -17757,7 +17754,7 @@
         <v>102</v>
       </c>
       <c r="C531" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D531" s="20">
         <v>2014</v>
@@ -17789,7 +17786,7 @@
         <v>103</v>
       </c>
       <c r="C532" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D532" s="20">
         <v>2014</v>
@@ -17821,7 +17818,7 @@
         <v>151</v>
       </c>
       <c r="C533" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D533" s="20">
         <v>2014</v>
@@ -17853,7 +17850,7 @@
         <v>153</v>
       </c>
       <c r="C534" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D534" s="20">
         <v>2014</v>
@@ -17885,7 +17882,7 @@
         <v>154</v>
       </c>
       <c r="C535" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D535" s="20">
         <v>2014</v>
@@ -17917,7 +17914,7 @@
         <v>155</v>
       </c>
       <c r="C536" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D536" s="20">
         <v>2014</v>
@@ -17949,7 +17946,7 @@
         <v>157</v>
       </c>
       <c r="C537" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D537" s="20">
         <v>2014</v>
@@ -17981,7 +17978,7 @@
         <v>158</v>
       </c>
       <c r="C538" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D538" s="20">
         <v>2014</v>
@@ -18013,7 +18010,7 @@
         <v>159</v>
       </c>
       <c r="C539" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D539" s="20">
         <v>2014</v>
@@ -18045,7 +18042,7 @@
         <v>1</v>
       </c>
       <c r="C540" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D540" s="16">
         <v>2014</v>
@@ -18077,7 +18074,7 @@
         <v>241</v>
       </c>
       <c r="C541" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D541" s="20">
         <v>2014</v>
@@ -18109,7 +18106,7 @@
         <v>241001</v>
       </c>
       <c r="C542" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D542" s="20">
         <v>2014</v>
@@ -18141,7 +18138,7 @@
         <v>241999</v>
       </c>
       <c r="C543" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D543" s="20">
         <v>2014</v>
@@ -18173,7 +18170,7 @@
         <v>251</v>
       </c>
       <c r="C544" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D544" s="20">
         <v>2014</v>
@@ -18205,7 +18202,7 @@
         <v>252</v>
       </c>
       <c r="C545" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D545" s="20">
         <v>2014</v>
@@ -18237,7 +18234,7 @@
         <v>254</v>
       </c>
       <c r="C546" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D546" s="20">
         <v>2014</v>
@@ -18269,7 +18266,7 @@
         <v>255</v>
       </c>
       <c r="C547" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D547" s="20">
         <v>2014</v>
@@ -18301,7 +18298,7 @@
         <v>256</v>
       </c>
       <c r="C548" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D548" s="20">
         <v>2014</v>
@@ -18333,7 +18330,7 @@
         <v>257</v>
       </c>
       <c r="C549" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D549" s="20">
         <v>2014</v>
@@ -18365,7 +18362,7 @@
         <v>2</v>
       </c>
       <c r="C550" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D550" s="16">
         <v>2014</v>
@@ -18397,7 +18394,7 @@
         <v>351</v>
       </c>
       <c r="C551" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D551" s="20">
         <v>2014</v>
@@ -18429,7 +18426,7 @@
         <v>352</v>
       </c>
       <c r="C552" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D552" s="20">
         <v>2014</v>
@@ -18461,7 +18458,7 @@
         <v>353</v>
       </c>
       <c r="C553" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D553" s="20">
         <v>2014</v>
@@ -18493,7 +18490,7 @@
         <v>12</v>
       </c>
       <c r="C554" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D554" s="20">
         <v>2014</v>
@@ -18525,7 +18522,7 @@
         <v>355</v>
       </c>
       <c r="C555" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D555" s="20">
         <v>2014</v>
@@ -18557,7 +18554,7 @@
         <v>356</v>
       </c>
       <c r="C556" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D556" s="20">
         <v>2014</v>
@@ -18589,7 +18586,7 @@
         <v>357</v>
       </c>
       <c r="C557" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D557" s="20">
         <v>2014</v>
@@ -18621,7 +18618,7 @@
         <v>358</v>
       </c>
       <c r="C558" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D558" s="20">
         <v>2014</v>
@@ -18653,7 +18650,7 @@
         <v>359</v>
       </c>
       <c r="C559" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D559" s="20">
         <v>2014</v>
@@ -18685,7 +18682,7 @@
         <v>12</v>
       </c>
       <c r="C560" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D560" s="20">
         <v>2014</v>
@@ -18717,7 +18714,7 @@
         <v>361</v>
       </c>
       <c r="C561" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D561" s="20">
         <v>2014</v>
@@ -18749,7 +18746,7 @@
         <v>3</v>
       </c>
       <c r="C562" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D562" s="16">
         <v>2014</v>
@@ -18781,7 +18778,7 @@
         <v>401</v>
       </c>
       <c r="C563" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D563" s="20">
         <v>2014</v>
@@ -18813,7 +18810,7 @@
         <v>13</v>
       </c>
       <c r="C564" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D564" s="20">
         <v>2014</v>
@@ -18845,7 +18842,7 @@
         <v>403</v>
       </c>
       <c r="C565" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D565" s="20">
         <v>2014</v>
@@ -18877,7 +18874,7 @@
         <v>404</v>
       </c>
       <c r="C566" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D566" s="20">
         <v>2014</v>
@@ -18909,7 +18906,7 @@
         <v>405</v>
       </c>
       <c r="C567" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D567" s="20">
         <v>2014</v>
@@ -18941,7 +18938,7 @@
         <v>451</v>
       </c>
       <c r="C568" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D568" s="20">
         <v>2014</v>
@@ -18973,7 +18970,7 @@
         <v>452</v>
       </c>
       <c r="C569" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D569" s="20">
         <v>2014</v>
@@ -19005,7 +19002,7 @@
         <v>453</v>
       </c>
       <c r="C570" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D570" s="20">
         <v>2014</v>
@@ -19037,7 +19034,7 @@
         <v>454</v>
       </c>
       <c r="C571" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D571" s="20">
         <v>2014</v>
@@ -19069,7 +19066,7 @@
         <v>14</v>
       </c>
       <c r="C572" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D572" s="20">
         <v>2014</v>
@@ -19101,7 +19098,7 @@
         <v>456</v>
       </c>
       <c r="C573" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D573" s="20">
         <v>2014</v>
@@ -19133,7 +19130,7 @@
         <v>13</v>
       </c>
       <c r="C574" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D574" s="20">
         <v>2014</v>
@@ -19165,7 +19162,7 @@
         <v>458</v>
       </c>
       <c r="C575" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D575" s="20">
         <v>2014</v>
@@ -19197,7 +19194,7 @@
         <v>459</v>
       </c>
       <c r="C576" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D576" s="20">
         <v>2014</v>
@@ -19229,7 +19226,7 @@
         <v>460</v>
       </c>
       <c r="C577" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D577" s="20">
         <v>2014</v>
@@ -19261,7 +19258,7 @@
         <v>461</v>
       </c>
       <c r="C578" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D578" s="20">
         <v>2014</v>
@@ -19293,7 +19290,7 @@
         <v>14</v>
       </c>
       <c r="C579" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D579" s="20">
         <v>2014</v>
@@ -19325,7 +19322,7 @@
         <v>4</v>
       </c>
       <c r="C580" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D580" s="16">
         <v>2014</v>
@@ -19357,7 +19354,7 @@
         <v>0</v>
       </c>
       <c r="C581" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D581" s="16">
         <v>2014</v>
@@ -19389,7 +19386,7 @@
         <v>101</v>
       </c>
       <c r="C582" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D582" s="20">
         <v>2013</v>
@@ -19421,7 +19418,7 @@
         <v>102</v>
       </c>
       <c r="C583" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D583" s="20">
         <v>2013</v>
@@ -19453,7 +19450,7 @@
         <v>103</v>
       </c>
       <c r="C584" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D584" s="20">
         <v>2013</v>
@@ -19485,7 +19482,7 @@
         <v>151</v>
       </c>
       <c r="C585" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D585" s="20">
         <v>2013</v>
@@ -19517,7 +19514,7 @@
         <v>153</v>
       </c>
       <c r="C586" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D586" s="20">
         <v>2013</v>
@@ -19549,7 +19546,7 @@
         <v>154</v>
       </c>
       <c r="C587" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D587" s="20">
         <v>2013</v>
@@ -19581,7 +19578,7 @@
         <v>155</v>
       </c>
       <c r="C588" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D588" s="20">
         <v>2013</v>
@@ -19613,7 +19610,7 @@
         <v>157</v>
       </c>
       <c r="C589" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D589" s="20">
         <v>2013</v>
@@ -19645,7 +19642,7 @@
         <v>158</v>
       </c>
       <c r="C590" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D590" s="20">
         <v>2013</v>
@@ -19677,7 +19674,7 @@
         <v>159</v>
       </c>
       <c r="C591" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D591" s="20">
         <v>2013</v>
@@ -19709,7 +19706,7 @@
         <v>1</v>
       </c>
       <c r="C592" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D592" s="16">
         <v>2013</v>
@@ -19741,7 +19738,7 @@
         <v>241</v>
       </c>
       <c r="C593" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D593" s="20">
         <v>2013</v>
@@ -19773,7 +19770,7 @@
         <v>241001</v>
       </c>
       <c r="C594" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D594" s="20">
         <v>2013</v>
@@ -19805,7 +19802,7 @@
         <v>241999</v>
       </c>
       <c r="C595" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D595" s="20">
         <v>2013</v>
@@ -19837,7 +19834,7 @@
         <v>251</v>
       </c>
       <c r="C596" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D596" s="20">
         <v>2013</v>
@@ -19869,7 +19866,7 @@
         <v>252</v>
       </c>
       <c r="C597" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D597" s="20">
         <v>2013</v>
@@ -19901,7 +19898,7 @@
         <v>254</v>
       </c>
       <c r="C598" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D598" s="20">
         <v>2013</v>
@@ -19933,7 +19930,7 @@
         <v>255</v>
       </c>
       <c r="C599" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D599" s="20">
         <v>2013</v>
@@ -19965,7 +19962,7 @@
         <v>256</v>
       </c>
       <c r="C600" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D600" s="20">
         <v>2013</v>
@@ -19997,7 +19994,7 @@
         <v>257</v>
       </c>
       <c r="C601" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D601" s="20">
         <v>2013</v>
@@ -20029,7 +20026,7 @@
         <v>2</v>
       </c>
       <c r="C602" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D602" s="16">
         <v>2013</v>
@@ -20061,7 +20058,7 @@
         <v>351</v>
       </c>
       <c r="C603" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D603" s="20">
         <v>2013</v>
@@ -20093,7 +20090,7 @@
         <v>352</v>
       </c>
       <c r="C604" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D604" s="20">
         <v>2013</v>
@@ -20125,7 +20122,7 @@
         <v>353</v>
       </c>
       <c r="C605" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D605" s="20">
         <v>2013</v>
@@ -20157,7 +20154,7 @@
         <v>12</v>
       </c>
       <c r="C606" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D606" s="20">
         <v>2013</v>
@@ -20189,7 +20186,7 @@
         <v>355</v>
       </c>
       <c r="C607" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D607" s="20">
         <v>2013</v>
@@ -20221,7 +20218,7 @@
         <v>356</v>
       </c>
       <c r="C608" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D608" s="20">
         <v>2013</v>
@@ -20253,7 +20250,7 @@
         <v>357</v>
       </c>
       <c r="C609" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D609" s="20">
         <v>2013</v>
@@ -20285,7 +20282,7 @@
         <v>358</v>
       </c>
       <c r="C610" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D610" s="20">
         <v>2013</v>
@@ -20317,7 +20314,7 @@
         <v>359</v>
       </c>
       <c r="C611" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D611" s="20">
         <v>2013</v>
@@ -20349,7 +20346,7 @@
         <v>12</v>
       </c>
       <c r="C612" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D612" s="20">
         <v>2013</v>
@@ -20381,7 +20378,7 @@
         <v>361</v>
       </c>
       <c r="C613" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D613" s="20">
         <v>2013</v>
@@ -20413,7 +20410,7 @@
         <v>3</v>
       </c>
       <c r="C614" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D614" s="16">
         <v>2013</v>
@@ -20445,7 +20442,7 @@
         <v>401</v>
       </c>
       <c r="C615" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D615" s="20">
         <v>2013</v>
@@ -20477,7 +20474,7 @@
         <v>13</v>
       </c>
       <c r="C616" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D616" s="20">
         <v>2013</v>
@@ -20509,7 +20506,7 @@
         <v>403</v>
       </c>
       <c r="C617" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D617" s="20">
         <v>2013</v>
@@ -20541,7 +20538,7 @@
         <v>404</v>
       </c>
       <c r="C618" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D618" s="20">
         <v>2013</v>
@@ -20573,7 +20570,7 @@
         <v>405</v>
       </c>
       <c r="C619" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D619" s="20">
         <v>2013</v>
@@ -20605,7 +20602,7 @@
         <v>451</v>
       </c>
       <c r="C620" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D620" s="20">
         <v>2013</v>
@@ -20637,7 +20634,7 @@
         <v>452</v>
       </c>
       <c r="C621" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D621" s="20">
         <v>2013</v>
@@ -20669,7 +20666,7 @@
         <v>453</v>
       </c>
       <c r="C622" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D622" s="20">
         <v>2013</v>
@@ -20701,7 +20698,7 @@
         <v>454</v>
       </c>
       <c r="C623" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D623" s="20">
         <v>2013</v>
@@ -20733,7 +20730,7 @@
         <v>14</v>
       </c>
       <c r="C624" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D624" s="20">
         <v>2013</v>
@@ -20765,7 +20762,7 @@
         <v>456</v>
       </c>
       <c r="C625" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D625" s="20">
         <v>2013</v>
@@ -20797,7 +20794,7 @@
         <v>13</v>
       </c>
       <c r="C626" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D626" s="20">
         <v>2013</v>
@@ -20829,7 +20826,7 @@
         <v>458</v>
       </c>
       <c r="C627" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D627" s="20">
         <v>2013</v>
@@ -20861,7 +20858,7 @@
         <v>459</v>
       </c>
       <c r="C628" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D628" s="20">
         <v>2013</v>
@@ -20893,7 +20890,7 @@
         <v>460</v>
       </c>
       <c r="C629" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D629" s="20">
         <v>2013</v>
@@ -20925,7 +20922,7 @@
         <v>461</v>
       </c>
       <c r="C630" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D630" s="20">
         <v>2013</v>
@@ -20957,7 +20954,7 @@
         <v>14</v>
       </c>
       <c r="C631" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D631" s="20">
         <v>2013</v>
@@ -20989,7 +20986,7 @@
         <v>4</v>
       </c>
       <c r="C632" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D632" s="16">
         <v>2013</v>
@@ -21021,7 +21018,7 @@
         <v>0</v>
       </c>
       <c r="C633" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D633" s="16">
         <v>2013</v>
@@ -21053,7 +21050,7 @@
         <v>101</v>
       </c>
       <c r="C634" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D634" s="20">
         <v>2012</v>
@@ -21085,7 +21082,7 @@
         <v>102</v>
       </c>
       <c r="C635" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D635" s="20">
         <v>2012</v>
@@ -21117,7 +21114,7 @@
         <v>103</v>
       </c>
       <c r="C636" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D636" s="20">
         <v>2012</v>
@@ -21149,7 +21146,7 @@
         <v>151</v>
       </c>
       <c r="C637" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D637" s="20">
         <v>2012</v>
@@ -21181,7 +21178,7 @@
         <v>153</v>
       </c>
       <c r="C638" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D638" s="20">
         <v>2012</v>
@@ -21213,7 +21210,7 @@
         <v>154</v>
       </c>
       <c r="C639" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D639" s="20">
         <v>2012</v>
@@ -21245,7 +21242,7 @@
         <v>155</v>
       </c>
       <c r="C640" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D640" s="20">
         <v>2012</v>
@@ -21277,7 +21274,7 @@
         <v>157</v>
       </c>
       <c r="C641" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D641" s="20">
         <v>2012</v>
@@ -21309,7 +21306,7 @@
         <v>159</v>
       </c>
       <c r="C642" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D642" s="20">
         <v>2012</v>
@@ -21341,7 +21338,7 @@
         <v>158</v>
       </c>
       <c r="C643" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D643" s="20">
         <v>2012</v>
@@ -21373,7 +21370,7 @@
         <v>1</v>
       </c>
       <c r="C644" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D644" s="16">
         <v>2012</v>
@@ -21405,7 +21402,7 @@
         <v>241</v>
       </c>
       <c r="C645" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D645" s="20">
         <v>2012</v>
@@ -21437,7 +21434,7 @@
         <v>241001</v>
       </c>
       <c r="C646" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D646" s="20">
         <v>2012</v>
@@ -21469,7 +21466,7 @@
         <v>241999</v>
       </c>
       <c r="C647" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D647" s="20">
         <v>2012</v>
@@ -21501,7 +21498,7 @@
         <v>251</v>
       </c>
       <c r="C648" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D648" s="20">
         <v>2012</v>
@@ -21533,7 +21530,7 @@
         <v>252</v>
       </c>
       <c r="C649" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D649" s="20">
         <v>2012</v>
@@ -21565,7 +21562,7 @@
         <v>254</v>
       </c>
       <c r="C650" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D650" s="20">
         <v>2012</v>
@@ -21597,7 +21594,7 @@
         <v>255</v>
       </c>
       <c r="C651" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D651" s="20">
         <v>2012</v>
@@ -21629,7 +21626,7 @@
         <v>256</v>
       </c>
       <c r="C652" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D652" s="20">
         <v>2012</v>
@@ -21661,7 +21658,7 @@
         <v>257</v>
       </c>
       <c r="C653" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D653" s="20">
         <v>2012</v>
@@ -21693,7 +21690,7 @@
         <v>2</v>
       </c>
       <c r="C654" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D654" s="16">
         <v>2012</v>
@@ -21725,7 +21722,7 @@
         <v>351</v>
       </c>
       <c r="C655" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D655" s="20">
         <v>2012</v>
@@ -21757,7 +21754,7 @@
         <v>352</v>
       </c>
       <c r="C656" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D656" s="20">
         <v>2012</v>
@@ -21789,7 +21786,7 @@
         <v>353</v>
       </c>
       <c r="C657" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D657" s="20">
         <v>2012</v>
@@ -21821,7 +21818,7 @@
         <v>12</v>
       </c>
       <c r="C658" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D658" s="20">
         <v>2012</v>
@@ -21853,7 +21850,7 @@
         <v>355</v>
       </c>
       <c r="C659" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D659" s="20">
         <v>2012</v>
@@ -21885,7 +21882,7 @@
         <v>356</v>
       </c>
       <c r="C660" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D660" s="20">
         <v>2012</v>
@@ -21917,7 +21914,7 @@
         <v>357</v>
       </c>
       <c r="C661" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D661" s="20">
         <v>2012</v>
@@ -21949,7 +21946,7 @@
         <v>358</v>
       </c>
       <c r="C662" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D662" s="20">
         <v>2012</v>
@@ -21981,7 +21978,7 @@
         <v>359</v>
       </c>
       <c r="C663" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D663" s="20">
         <v>2012</v>
@@ -22013,7 +22010,7 @@
         <v>12</v>
       </c>
       <c r="C664" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D664" s="20">
         <v>2012</v>
@@ -22045,7 +22042,7 @@
         <v>361</v>
       </c>
       <c r="C665" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D665" s="20">
         <v>2012</v>
@@ -22077,7 +22074,7 @@
         <v>3</v>
       </c>
       <c r="C666" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D666" s="16">
         <v>2012</v>
@@ -22109,7 +22106,7 @@
         <v>401</v>
       </c>
       <c r="C667" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D667" s="20">
         <v>2012</v>
@@ -22141,7 +22138,7 @@
         <v>13</v>
       </c>
       <c r="C668" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D668" s="20">
         <v>2012</v>
@@ -22173,7 +22170,7 @@
         <v>403</v>
       </c>
       <c r="C669" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D669" s="20">
         <v>2012</v>
@@ -22205,7 +22202,7 @@
         <v>404</v>
       </c>
       <c r="C670" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D670" s="20">
         <v>2012</v>
@@ -22237,7 +22234,7 @@
         <v>405</v>
       </c>
       <c r="C671" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D671" s="20">
         <v>2012</v>
@@ -22269,7 +22266,7 @@
         <v>451</v>
       </c>
       <c r="C672" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D672" s="20">
         <v>2012</v>
@@ -22301,7 +22298,7 @@
         <v>452</v>
       </c>
       <c r="C673" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D673" s="20">
         <v>2012</v>
@@ -22333,7 +22330,7 @@
         <v>453</v>
       </c>
       <c r="C674" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D674" s="20">
         <v>2012</v>
@@ -22365,7 +22362,7 @@
         <v>454</v>
       </c>
       <c r="C675" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D675" s="20">
         <v>2012</v>
@@ -22397,7 +22394,7 @@
         <v>14</v>
       </c>
       <c r="C676" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D676" s="20">
         <v>2012</v>
@@ -22429,7 +22426,7 @@
         <v>456</v>
       </c>
       <c r="C677" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D677" s="20">
         <v>2012</v>
@@ -22461,7 +22458,7 @@
         <v>13</v>
       </c>
       <c r="C678" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D678" s="20">
         <v>2012</v>
@@ -22493,7 +22490,7 @@
         <v>458</v>
       </c>
       <c r="C679" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D679" s="20">
         <v>2012</v>
@@ -22525,7 +22522,7 @@
         <v>459</v>
       </c>
       <c r="C680" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D680" s="20">
         <v>2012</v>
@@ -22557,7 +22554,7 @@
         <v>460</v>
       </c>
       <c r="C681" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D681" s="20">
         <v>2012</v>
@@ -22589,7 +22586,7 @@
         <v>461</v>
       </c>
       <c r="C682" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D682" s="20">
         <v>2012</v>
@@ -22621,7 +22618,7 @@
         <v>14</v>
       </c>
       <c r="C683" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D683" s="20">
         <v>2012</v>
@@ -22653,7 +22650,7 @@
         <v>4</v>
       </c>
       <c r="C684" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D684" s="20">
         <v>2012</v>
@@ -22685,7 +22682,7 @@
         <v>0</v>
       </c>
       <c r="C685" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D685" s="20">
         <v>2012</v>
@@ -22717,7 +22714,7 @@
         <v>101</v>
       </c>
       <c r="C686" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D686" s="20">
         <v>2011</v>
@@ -22749,7 +22746,7 @@
         <v>102</v>
       </c>
       <c r="C687" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D687" s="20">
         <v>2011</v>
@@ -22781,7 +22778,7 @@
         <v>103</v>
       </c>
       <c r="C688" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D688" s="20">
         <v>2011</v>
@@ -22813,7 +22810,7 @@
         <v>151</v>
       </c>
       <c r="C689" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D689" s="20">
         <v>2011</v>
@@ -22845,7 +22842,7 @@
         <v>153</v>
       </c>
       <c r="C690" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D690" s="20">
         <v>2011</v>
@@ -22877,7 +22874,7 @@
         <v>154</v>
       </c>
       <c r="C691" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D691" s="20">
         <v>2011</v>
@@ -22909,7 +22906,7 @@
         <v>155</v>
       </c>
       <c r="C692" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D692" s="20">
         <v>2011</v>
@@ -22941,7 +22938,7 @@
         <v>157</v>
       </c>
       <c r="C693" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D693" s="20">
         <v>2011</v>
@@ -22973,7 +22970,7 @@
         <v>158</v>
       </c>
       <c r="C694" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D694" s="20">
         <v>2011</v>
@@ -23005,7 +23002,7 @@
         <v>159</v>
       </c>
       <c r="C695" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D695" s="20">
         <v>2011</v>
@@ -23037,7 +23034,7 @@
         <v>1</v>
       </c>
       <c r="C696" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D696" s="20">
         <v>2011</v>
@@ -23069,7 +23066,7 @@
         <v>241</v>
       </c>
       <c r="C697" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D697" s="20">
         <v>2011</v>
@@ -23101,7 +23098,7 @@
         <v>241001</v>
       </c>
       <c r="C698" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D698" s="20">
         <v>2011</v>
@@ -23133,7 +23130,7 @@
         <v>241999</v>
       </c>
       <c r="C699" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D699" s="20">
         <v>2011</v>
@@ -23165,7 +23162,7 @@
         <v>251</v>
       </c>
       <c r="C700" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D700" s="20">
         <v>2011</v>
@@ -23197,7 +23194,7 @@
         <v>252</v>
       </c>
       <c r="C701" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D701" s="20">
         <v>2011</v>
@@ -23229,7 +23226,7 @@
         <v>254</v>
       </c>
       <c r="C702" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D702" s="20">
         <v>2011</v>
@@ -23261,7 +23258,7 @@
         <v>255</v>
       </c>
       <c r="C703" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D703" s="20">
         <v>2011</v>
@@ -23293,7 +23290,7 @@
         <v>256</v>
       </c>
       <c r="C704" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D704" s="20">
         <v>2011</v>
@@ -23325,7 +23322,7 @@
         <v>257</v>
       </c>
       <c r="C705" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D705" s="20">
         <v>2011</v>
@@ -23357,7 +23354,7 @@
         <v>2</v>
       </c>
       <c r="C706" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D706" s="20">
         <v>2011</v>
@@ -23389,7 +23386,7 @@
         <v>351</v>
       </c>
       <c r="C707" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D707" s="20">
         <v>2011</v>
@@ -23421,7 +23418,7 @@
         <v>352</v>
       </c>
       <c r="C708" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D708" s="20">
         <v>2011</v>
@@ -23453,7 +23450,7 @@
         <v>353</v>
       </c>
       <c r="C709" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D709" s="20">
         <v>2011</v>
@@ -23485,7 +23482,7 @@
         <v>12</v>
       </c>
       <c r="C710" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D710" s="20">
         <v>2011</v>
@@ -23517,7 +23514,7 @@
         <v>355</v>
       </c>
       <c r="C711" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D711" s="20">
         <v>2011</v>
@@ -23549,7 +23546,7 @@
         <v>356</v>
       </c>
       <c r="C712" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D712" s="20">
         <v>2011</v>
@@ -23581,7 +23578,7 @@
         <v>357</v>
       </c>
       <c r="C713" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D713" s="20">
         <v>2011</v>
@@ -23613,7 +23610,7 @@
         <v>358</v>
       </c>
       <c r="C714" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D714" s="20">
         <v>2011</v>
@@ -23645,7 +23642,7 @@
         <v>359</v>
       </c>
       <c r="C715" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D715" s="20">
         <v>2011</v>
@@ -23677,7 +23674,7 @@
         <v>12</v>
       </c>
       <c r="C716" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D716" s="20">
         <v>2011</v>
@@ -23709,7 +23706,7 @@
         <v>361</v>
       </c>
       <c r="C717" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D717" s="20">
         <v>2011</v>
@@ -23741,7 +23738,7 @@
         <v>3</v>
       </c>
       <c r="C718" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D718" s="20">
         <v>2011</v>
@@ -23773,7 +23770,7 @@
         <v>401</v>
       </c>
       <c r="C719" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D719" s="20">
         <v>2011</v>
@@ -23805,7 +23802,7 @@
         <v>13</v>
       </c>
       <c r="C720" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D720" s="20">
         <v>2011</v>
@@ -23837,7 +23834,7 @@
         <v>403</v>
       </c>
       <c r="C721" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D721" s="20">
         <v>2011</v>
@@ -23869,7 +23866,7 @@
         <v>404</v>
       </c>
       <c r="C722" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D722" s="20">
         <v>2011</v>
@@ -23901,7 +23898,7 @@
         <v>405</v>
       </c>
       <c r="C723" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D723" s="20">
         <v>2011</v>
@@ -23933,7 +23930,7 @@
         <v>451</v>
       </c>
       <c r="C724" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D724" s="20">
         <v>2011</v>
@@ -23965,7 +23962,7 @@
         <v>452</v>
       </c>
       <c r="C725" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D725" s="20">
         <v>2011</v>
@@ -23997,7 +23994,7 @@
         <v>453</v>
       </c>
       <c r="C726" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D726" s="20">
         <v>2011</v>
@@ -24029,7 +24026,7 @@
         <v>454</v>
       </c>
       <c r="C727" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D727" s="20">
         <v>2011</v>
@@ -24061,7 +24058,7 @@
         <v>14</v>
       </c>
       <c r="C728" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D728" s="20">
         <v>2011</v>
@@ -24093,7 +24090,7 @@
         <v>456</v>
       </c>
       <c r="C729" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D729" s="20">
         <v>2011</v>
@@ -24125,7 +24122,7 @@
         <v>13</v>
       </c>
       <c r="C730" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D730" s="20">
         <v>2011</v>
@@ -24157,7 +24154,7 @@
         <v>458</v>
       </c>
       <c r="C731" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D731" s="20">
         <v>2011</v>
@@ -24189,7 +24186,7 @@
         <v>459</v>
       </c>
       <c r="C732" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D732" s="20">
         <v>2011</v>
@@ -24221,7 +24218,7 @@
         <v>460</v>
       </c>
       <c r="C733" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D733" s="20">
         <v>2011</v>
@@ -24253,7 +24250,7 @@
         <v>461</v>
       </c>
       <c r="C734" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D734" s="20">
         <v>2011</v>
@@ -24285,7 +24282,7 @@
         <v>14</v>
       </c>
       <c r="C735" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D735" s="20">
         <v>2011</v>
@@ -24317,7 +24314,7 @@
         <v>4</v>
       </c>
       <c r="C736" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D736" s="20">
         <v>2011</v>
@@ -24344,12 +24341,12 @@
         <v>17.239999999999998</v>
       </c>
     </row>
-    <row r="737" spans="2:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="2:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B737" s="19">
         <v>0</v>
       </c>
       <c r="C737" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D737" s="20">
         <v>2011</v>
@@ -24376,63 +24373,100 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="738" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C738" s="30"/>
-    </row>
-    <row r="739" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C739" s="24" t="s">
+    <row r="738" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C738" s="28"/>
+    </row>
+    <row r="739" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C739" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D739" s="38"/>
+      <c r="E739" s="38"/>
+      <c r="F739" s="38"/>
+      <c r="G739" s="38"/>
+      <c r="H739" s="38"/>
+      <c r="I739" s="38"/>
+      <c r="J739" s="38"/>
+      <c r="K739" s="38"/>
+      <c r="L739" s="38"/>
+      <c r="M739" s="38"/>
+      <c r="N739" s="38"/>
+    </row>
+    <row r="740" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C740" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="D740" s="38"/>
+      <c r="E740" s="38"/>
+      <c r="F740" s="38"/>
+      <c r="G740" s="38"/>
+      <c r="H740" s="38"/>
+      <c r="I740" s="38"/>
+      <c r="J740" s="38"/>
+      <c r="K740" s="38"/>
+      <c r="L740" s="38"/>
+      <c r="M740" s="38"/>
+      <c r="N740" s="38"/>
+    </row>
+    <row r="741" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C741" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="D741" s="38"/>
+      <c r="E741" s="38"/>
+      <c r="F741" s="38"/>
+      <c r="G741" s="38"/>
+      <c r="H741" s="38"/>
+      <c r="I741" s="38"/>
+      <c r="J741" s="38"/>
+      <c r="K741" s="38"/>
+      <c r="L741" s="38"/>
+      <c r="M741" s="38"/>
+      <c r="N741" s="38"/>
+    </row>
+    <row r="742" spans="2:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C742" s="23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="740" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C740" s="25" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="741" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C741" s="25" t="s">
+    <row r="743" spans="2:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C743" s="26"/>
+    </row>
+    <row r="744" spans="2:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C744" s="25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="745" spans="2:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" spans="2:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C746" s="24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="747" spans="2:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C747" s="24" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="742" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C742" s="23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="743" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C743" s="28"/>
-    </row>
-    <row r="744" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C744" s="27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="746" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="C746" s="26" t="s">
+    <row r="748" spans="2:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C748" s="24" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="747" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="C747" s="26" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="748" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="C748" s="26" t="s">
+    <row r="749" spans="2:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C749" s="27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="749" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="C749" s="29" t="s">
-        <v>21</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="C740:N740"/>
+    <mergeCell ref="C741:N741"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="I7:K7"/>
+    <mergeCell ref="C739:N739"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B742" r:id="rId1" display="https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Haushalte-Familien/Methoden/mikrozensus-2020.html" xr:uid="{211BF84A-1D3B-42B6-93E4-133DEF5CCC5B}"/>
